--- a/public/StageStepTable.xlsx
+++ b/public/StageStepTable.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -405,10 +401,10 @@
   <cols>
     <col min="2" max="2" customWidth="1" width="11.75"/>
     <col min="3" max="3" customWidth="1" width="11.75"/>
-    <col min="4" max="4" customWidth="1" width="43.125"/>
-    <col min="5" max="5" customWidth="1" width="52.625"/>
-    <col min="6" max="6" customWidth="1" width="52.625"/>
-    <col min="7" max="7" customWidth="1" width="76.3303571428571"/>
+    <col min="4" max="4" customWidth="1" width="9.875"/>
+    <col min="5" max="5" customWidth="1" width="16.25"/>
+    <col min="6" max="6" customWidth="1" width="13.125"/>
+    <col min="7" max="7" customWidth="1" width="76.375"/>
     <col min="8" max="8" customWidth="1" width="11.75"/>
     <col min="9" max="9" customWidth="1" width="11.75"/>
     <col min="10" max="10" customWidth="1" width="11.75"/>
@@ -536,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>[[10002,1,0],[20001,1,2.16],[30002,1,3.81],[40008,1,5.65]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -565,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>[[10002,1,0],[20001,1,1.96],[30002,1,3.97],[40008,1,5.6]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I6">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -594,13 +590,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>[[10002,1,0],[20001,1,1.9],[30002,1,4],[40008,1,5.97]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H7">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I7">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -623,13 +619,13 @@
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>[[10002,1,0],[20001,1,2.32],[30002,1,4.29],[40008,1,5.98]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H8">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I8">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -652,13 +648,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>[[10002,1,0],[20001,1,2.09],[30002,1,3.72],[40008,1,5.9]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H9">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I9">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -681,13 +677,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>[[10002,1,0],[20001,1,1.82],[30002,1,3.85],[40004,1,5.96]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H10">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I10">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -710,13 +706,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>[[10002,1,0],[10001,1,1.61],[20001,1,3.87],[30002,1,5.92],[40004,1,7.86]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I11">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -739,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="str">
-        <v>[[10002,1,0],[10001,1,1.69],[20001,1,3.47],[30002,1,5.22],[40004,1,7.46]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H12">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I12">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -768,16 +764,15 @@
         <v>0</v>
       </c>
       <c r="G13" t="str">
-        <v>[[10002,1,0],[10001,1,1.76],[20001,1,3.38],[30002,1,5.04],[40004,1,6.98]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H13">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I13">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J13">
-        <f>I13</f>
         <v>1</v>
       </c>
     </row>
@@ -798,16 +793,15 @@
         <v>1</v>
       </c>
       <c r="G14" t="str">
-        <v>[[90033,1,0],[90034,1,2.69],[10001,1,4.91],[10002,1,6.66],[10003,1,8.62],[20001,1,10.5],[30002,1,12.78],[40004,1,14.49]]</v>
+        <v>[[90033,1],[90034,1],[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H14">
-        <v>0.4</v>
+        <v>0.79</v>
       </c>
       <c r="I14">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="J14">
-        <f>I14</f>
         <v>1</v>
       </c>
     </row>
@@ -828,16 +822,15 @@
         <v>0</v>
       </c>
       <c r="G15" t="str">
-        <v>[[10001,1,0],[10002,1,2.02],[20001,1,4.27],[30002,1,6.17],[40004,1,7.82]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H15">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I15">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J15">
-        <f>I15</f>
         <v>1</v>
       </c>
     </row>
@@ -858,13 +851,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="str">
-        <v>[[10001,1,0],[10002,1,1.64],[20001,1,3.96],[30002,1,6.29],[40004,1,8.61]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H16">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I16">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -887,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="str">
-        <v>[[10001,1,0],[10002,1,1.89],[20001,1,4.27],[30002,1,6.66],[40004,1,8.36]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H17">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I17">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -916,13 +909,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="str">
-        <v>[[10001,1,0],[10002,1,2.22],[10007,1,4.43],[20001,1,6.73],[30002,1,8.59],[40004,1,10.45]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H18">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I18">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -945,13 +938,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="str">
-        <v>[[10001,1,0],[10007,1,2.08],[10002,1,4.05],[20001,1,6.33],[30002,1,8.4],[40004,1,10.61]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H19">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I19">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -974,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>[[10001,1,0],[10007,1,2.18],[10002,1,4.32],[20001,1,6.35],[30002,1,8.44],[40004,1,10.37]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H20">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I20">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1003,13 +996,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>[[10001,1,0],[10007,1,2.1],[10002,1,4.06],[20001,1,5.96],[30002,1,7.85],[40004,1,9.76]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H21">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I21">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1032,13 +1025,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>[[10001,1,0],[10007,1,2.32],[10002,1,4.41],[20001,1,6.15],[30002,1,8.33],[40004,1,10.69]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H22">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I22">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1061,13 +1054,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>[[10001,1,0],[10007,1,1.67],[10002,1,3.93],[20001,1,5.86],[20003,1,7.55],[30002,1,9.53],[30008,1,11.74],[40004,1,13.6]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H23">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="I23">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1090,13 +1083,13 @@
         <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v>[[90033,1,0],[90034,1,2.85],[10001,1,5.77],[10002,1,7.55],[10007,1,9.84],[10005,1,12.09],[10012,1,14.47],[20001,1,16.85],[20003,1,19.15],[30002,1,21.32],[30008,1,23],[40004,1,25.09],[40008,1,27.02]]</v>
+        <v>[[90033,1],[90034,1],[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H24">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="I24">
-        <v>0.47</v>
+        <v>0.94</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1119,13 +1112,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="str">
-        <v>[[10001,1,0],[10002,1,2.11],[10005,1,3.85],[20001,2,6.18],[30002,1,8.08],[40004,1,10.18]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H25">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I25">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1148,13 +1141,13 @@
         <v>0</v>
       </c>
       <c r="G26" t="str">
-        <v>[[10001,1,0],[10002,1,2.34],[10005,1,4.05],[10003,1,6.38],[20001,1,8.19],[20003,1,9.92],[30002,1,11.6],[30004,1,13.88],[40004,1,16.16]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H26">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I26">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1177,13 +1170,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="str">
-        <v>[[10001,1,0],[10002,1,1.89],[10005,1,3.51],[10003,1,5.27],[20001,1,7.24],[20003,1,9.37],[30002,1,11.3],[30004,1,13.6],[40004,1,15.73]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H27">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I27">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1206,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="str">
-        <v>[[10001,1,0],[10002,1,2.37],[10005,1,4.74],[10003,1,6.83],[20001,1,9.07],[20003,1,10.77],[30002,1,12.39],[30004,1,14.57],[40004,1,16.68]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H28">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I28">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1235,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="G29" t="str">
-        <v>[[10001,1,0],[10002,1,2.23],[10005,1,4],[10003,1,5.67],[20001,1,7.97],[20003,1,9.99],[30002,1,12.17],[30004,1,13.94],[40004,1,16.01]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H29">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I29">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1264,13 +1257,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="str">
-        <v>[[10001,1,0],[10002,1,1.75],[10005,1,3.78],[10003,1,5.98],[20001,1,7.93],[20003,1,10.02],[30002,1,11.68],[30004,1,13.29],[40004,1,15.07]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H30">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I30">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1293,13 +1286,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="str">
-        <v>[[10001,1,0],[10002,1,2.15],[10005,1,4.21],[10003,1,6.21],[20001,1,8.44],[20003,1,10.43],[30002,1,12.34],[30004,1,14.19],[40004,1,16.38]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H31">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I31">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1322,13 +1315,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="str">
-        <v>[[10001,1,0],[10002,1,1.7],[10005,1,3.81],[10003,1,6.06],[20001,1,7.89],[20003,1,10.18],[30002,1,12.26],[30004,1,14.55],[40004,1,16.37],[40008,1,18.02]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H32">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I32">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1351,13 +1344,13 @@
         <v>0</v>
       </c>
       <c r="G33" t="str">
-        <v>[[10001,1,0],[10002,1,2.22],[10005,1,4.42],[10003,1,6.11],[10007,1,8.08],[20001,1,10.17],[20003,1,12.11],[30002,1,14.47],[30004,1,16.48],[40004,1,18.13],[40008,1,20.12]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H33">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="I33">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1380,13 +1373,13 @@
         <v>1</v>
       </c>
       <c r="G34" t="str">
-        <v>[[90035,1,0],[90036,1,2.98],[10002,1,5.29],[10001,1,7.12],[10003,1,9.02],[10005,1,10.64],[10007,1,12.48],[10022,1,14.59],[20001,1,16.55],[20003,1,18.55],[20007,1,20.26],[30002,1,22.46],[30004,1,24.62],[30007,1,26.82],[40004,1,28.85],[40008,1,30.69]]</v>
+        <v>[[90035,1],[90036,1],[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H34">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="I34">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1409,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="G35" t="str">
-        <v>[[10022,1,0],[10001,1,2.23],[10002,1,4.45],[10005,1,6.23],[20001,1,7.94],[20007,1,10.2],[30002,1,12.16],[30004,1,14.55],[40004,1,16.23]]</v>
+        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H35">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I35">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -1438,13 +1431,13 @@
         <v>0</v>
       </c>
       <c r="G36" t="str">
-        <v>[[10022,1,0],[10001,1,1.97],[10002,1,4.33],[10005,1,6.19],[20001,1,8.09],[20007,1,10.03],[20004,1,12.3],[30002,1,14.41],[30004,1,16.49],[40004,1,18.28],[40001,1,20.34]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H36">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I36">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -1467,13 +1460,13 @@
         <v>0</v>
       </c>
       <c r="G37" t="str">
-        <v>[[10022,1,0],[10001,1,1.96],[10002,1,3.62],[10005,1,5.87],[20001,1,8.26],[20007,1,9.97],[20004,1,11.76],[30002,1,13.66],[30004,1,15.8],[40001,1,17.99],[40004,1,19.84]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H37">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I37">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -1496,13 +1489,13 @@
         <v>0</v>
       </c>
       <c r="G38" t="str">
-        <v>[[10022,1,0],[10001,1,2.11],[10002,1,4.31],[10005,1,6.01],[10003,1,8.12],[20001,1,10.36],[20007,1,12.49],[20004,1,14.16],[30002,1,16.31],[30004,1,18.43],[40001,1,20.32],[40004,1,22.06]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H38">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I38">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -1525,13 +1518,13 @@
         <v>0</v>
       </c>
       <c r="G39" t="str">
-        <v>[[10022,1,0],[10001,1,2.33],[10002,1,4.36],[10005,1,6.42],[10003,1,8.62],[20001,1,10.29],[20007,1,12.63],[20004,1,14.96],[30002,1,17.15],[30004,1,19.46],[40001,1,21.84],[40004,1,23.82]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H39">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I39">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -1554,13 +1547,13 @@
         <v>0</v>
       </c>
       <c r="G40" t="str">
-        <v>[[10022,1,0],[10001,1,1.83],[10002,1,3.96],[10005,1,6.12],[10003,1,8.24],[20001,1,10.13],[20007,1,11.84],[20004,1,14.2],[30002,1,16.52],[30004,1,18.46],[30008,1,20.12],[40001,1,21.88],[40004,1,23.95]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H40">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I40">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -1583,13 +1576,13 @@
         <v>0</v>
       </c>
       <c r="G41" t="str">
-        <v>[[10022,1,0],[10001,1,1.71],[10002,1,3.73],[10005,1,5.57],[10003,1,7.85],[20001,1,9.85],[20007,1,11.52],[20004,1,13.68],[30008,1,16.07],[30002,1,17.98],[30004,1,19.74],[40001,1,21.71],[40004,1,23.92]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H41">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I41">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -1612,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="str">
-        <v>[[10022,1,0],[10001,1,2.07],[10002,1,3.85],[10005,1,5.83],[10003,1,7.55],[20001,1,9.73],[20007,1,11.92],[20004,1,14.07],[30008,1,16.44],[30002,1,18.8],[30004,1,20.89],[40001,1,23.23],[40004,1,25.32]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H42">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I42">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -1641,13 +1634,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="str">
-        <v>[[10022,1,0],[10001,1,2.13],[10002,1,3.77],[10005,1,5.45],[10003,1,7.09],[10007,1,9.43],[20001,1,11.77],[20007,1,13.78],[20004,1,15.89],[30008,1,17.88],[30002,1,19.65],[30004,1,21.37],[40001,1,23.26],[40004,1,25.29]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H43">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I43">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -1670,13 +1663,13 @@
         <v>1</v>
       </c>
       <c r="G44" t="str">
-        <v>[[90035,1,0],[90036,1,2.73],[10022,1,5.01],[10001,1,7.16],[10002,1,9.37],[10005,1,10.97],[10007,1,12.87],[10003,1,14.6],[10015,1,16.41],[20001,1,18.29],[20007,1,20.14],[20004,1,22.08],[20003,1,24.37],[30002,1,26.53],[30008,1,28.24],[30004,1,30.2],[30007,1,32.06],[40004,1,33.84],[40001,1,35.47],[40008,1,37.2]]</v>
+        <v>[[90035,1],[90036,1],[10002,1],[10009,1],[10012,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H44">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="I44">
-        <v>0.57</v>
+        <v>1.14</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -1699,13 +1692,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="str">
-        <v>[[10022,1,0],[10015,1,1.98],[10001,1,4.2],[10002,1,6.53],[20001,1,8.52],[20003,1,10.86],[20007,1,13.06],[30002,1,15.38],[30007,1,17.34],[30008,1,19.17],[40004,1,21.31],[40008,1,23]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H45">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I45">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -1728,13 +1721,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="str">
-        <v>[[10022,1,0],[10015,1,2.33],[10001,1,4.11],[10002,1,5.78],[10005,1,8.02],[20001,1,9.77],[20003,1,11.69],[20007,1,13.67],[30002,1,15.74],[30007,1,17.68],[30008,1,19.77],[40004,1,21.41],[40008,1,23.02]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H46">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I46">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -1757,13 +1750,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="str">
-        <v>[[10022,1,0],[10015,1,1.98],[10001,1,4.25],[10002,1,6.35],[10005,1,8.39],[20001,1,10.54],[20003,1,12.84],[20007,1,15.2],[30002,1,17.41],[30007,1,19.17],[30008,1,21.37],[40004,1,23.53],[40008,1,25.41]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H47">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I47">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -1786,13 +1779,13 @@
         <v>0</v>
       </c>
       <c r="G48" t="str">
-        <v>[[10022,1,0],[10015,1,2.05],[10001,1,3.78],[10002,1,5.65],[10005,1,8.03],[20001,1,9.94],[20003,1,12.26],[20007,1,14.62],[30002,1,16.82],[30007,1,18.91],[30008,1,21.22],[40004,1,23.15],[40008,1,25.27],[40007,1,27.27]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H48">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I48">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -1815,13 +1808,13 @@
         <v>0</v>
       </c>
       <c r="G49" t="str">
-        <v>[[10022,1,0],[10015,1,1.99],[10001,1,4.2],[10002,1,5.84],[10005,1,7.66],[20001,1,9.33],[20003,1,11.59],[20007,1,13.44],[30002,1,15.28],[30007,1,17.57],[30008,1,19.64],[40004,1,21.84],[40007,1,23.95],[40008,1,25.91]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H49">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I49">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -1844,13 +1837,13 @@
         <v>0</v>
       </c>
       <c r="G50" t="str">
-        <v>[[10022,1,0],[10015,1,2.19],[10001,1,4.38],[10002,1,6.71],[10005,1,8.9],[20001,1,10.86],[20003,1,13.13],[20007,1,15.51],[30002,1,17.8],[30007,1,19.97],[30008,1,22.01],[40004,1,24.32],[40007,1,26.47],[40008,1,28.74]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H50">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I50">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -1873,13 +1866,13 @@
         <v>0</v>
       </c>
       <c r="G51" t="str">
-        <v>[[10022,1,0],[10015,1,1.71],[10001,1,3.59],[10002,1,5.67],[10005,1,7.53],[20001,1,9.36],[20003,1,11.45],[20007,1,13.74],[20004,1,16.05],[30002,1,18.34],[30007,1,20.69],[30008,1,22.76],[40004,1,25.14],[40007,1,27.06],[40008,1,28.8]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H51">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I51">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -1902,13 +1895,13 @@
         <v>0</v>
       </c>
       <c r="G52" t="str">
-        <v>[[10022,1,0],[10015,1,1.78],[10001,1,3.46],[10002,1,5.66],[10005,1,7.92],[20001,1,10.06],[20003,1,12.03],[20007,1,14.37],[20004,1,16.67],[30002,1,18.28],[30007,1,19.94],[30008,1,21.82],[40004,1,23.69],[40007,1,26.07],[40008,1,28.29]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H52">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I52">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -1931,13 +1924,13 @@
         <v>0</v>
       </c>
       <c r="G53" t="str">
-        <v>[[10022,1,0],[10015,1,2.29],[10001,1,4.31],[10002,1,6.1],[10005,1,8.02],[10014,1,9.68],[20001,1,11.68],[20003,1,13.57],[20007,1,15.25],[20004,1,16.94],[30002,1,18.77],[30007,1,20.62],[30008,1,22.85],[30004,1,24.47],[40004,1,26.21],[40007,1,27.95],[40008,1,29.71]]</v>
+        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
       </c>
       <c r="H53">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I53">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -1960,13 +1953,13 @@
         <v>1</v>
       </c>
       <c r="G54" t="str">
-        <v>[[90035,1,0],[90036,1,2.28],[10015,1,4.51],[10022,1,6.75],[10014,1,8.72],[10001,1,10.34],[10002,1,11.97],[10005,1,14.18],[10024,1,16.01],[10019,1,17.99],[20001,1,19.86],[20007,1,21.86],[20003,1,23.71],[20004,1,25.43],[20014,1,27.65],[30002,1,29.28],[30008,1,31.47],[30007,1,33.55],[30004,1,35.91],[30010,1,37.69],[40004,1,39.48],[40008,1,41.09],[40007,1,42.74],[40011,1,44.8]]</v>
+        <v>[[90035,1],[90036,1],[10002,1],[10009,1],[10014,1],[20002,1],[20004,1],[30004,1],[30007,1],[40001,1]]</v>
       </c>
       <c r="H54">
-        <v>0.68</v>
+        <v>1.35</v>
       </c>
       <c r="I54">
-        <v>0.77</v>
+        <v>1.55</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -1989,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="G55" t="str">
-        <v>[[10014,1,0],[10015,1,1.79],[10019,1,3.65],[10022,1,5.78],[20014,1,7.61],[20013,1,9.4],[30010,1,11.23],[30016,1,13.35],[40011,1,15.39]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H55">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I55">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2018,13 +2011,13 @@
         <v>0</v>
       </c>
       <c r="G56" t="str">
-        <v>[[10014,1,0],[10015,1,1.92],[10019,1,3.95],[10022,1,6.34],[20014,1,8.16],[20013,1,10.54],[30010,1,12.8],[30016,1,14.57],[40011,1,16.19],[40012,1,18.18]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H56">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I56">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2047,13 +2040,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="str">
-        <v>[[10014,1,0],[10015,1,1.94],[10019,1,3.93],[10022,1,5.9],[20014,1,7.64],[20013,1,9.28],[30010,1,11.04],[30016,1,13.37],[40011,1,15.02],[40012,1,16.79]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H57">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I57">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2076,13 +2069,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="str">
-        <v>[[10014,1,0],[10015,1,1.82],[10019,1,3.82],[10022,1,6.07],[10024,1,8.37],[20014,1,10],[20013,1,11.77],[30010,1,13.73],[30016,1,15.55],[40011,1,17.55],[40012,1,19.87]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H58">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I58">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -2105,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="str">
-        <v>[[10014,1,0],[10015,1,2.33],[10019,1,4.47],[10022,1,6.22],[10024,1,8.44],[20014,1,10.38],[20013,1,12.23],[30010,1,14.31],[30016,1,16.33],[40011,1,18.17],[40012,1,20.04]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H59">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I59">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -2134,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="str">
-        <v>[[10014,1,0],[10015,1,2.16],[10019,1,4.56],[10022,1,6.46],[10024,1,8.26],[20014,1,10.22],[20013,1,12.23],[30010,1,14.56],[30016,1,16.76],[40011,1,18.85],[40012,1,21.18]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H60">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I60">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -2163,13 +2156,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="str">
-        <v>[[10014,1,0],[10015,1,1.78],[10019,1,3.5],[10022,1,5.72],[10024,1,8.01],[20014,1,9.67],[20013,1,11.37],[30010,1,13.28],[30016,1,15.37],[40011,1,17.25],[40012,1,19.56]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H61">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I61">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -2192,13 +2185,13 @@
         <v>0</v>
       </c>
       <c r="G62" t="str">
-        <v>[[10014,1,0],[10015,1,2],[10019,1,4.26],[10022,1,6.28],[10024,1,8.02],[20014,1,9.84],[20013,1,12.18],[30010,1,14.4],[30016,1,16.44],[40011,1,18.23],[40012,1,20.34]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H62">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I62">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -2221,13 +2214,13 @@
         <v>0</v>
       </c>
       <c r="G63" t="str">
-        <v>[[10014,1,0],[10015,1,1.73],[10019,1,3.37],[10022,1,5.02],[10024,1,6.63],[20014,1,8.91],[20013,1,11.12],[30010,1,12.79],[30016,1,14.88],[40011,1,16.6],[40012,1,18.32]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H63">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="I63">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -2250,13 +2243,13 @@
         <v>1</v>
       </c>
       <c r="G64" t="str">
-        <v>[[90037,1,0],[90038,1,2.31],[10019,1,4.53],[10022,1,6.2],[10014,1,7.93],[10015,1,10.27],[10024,1,12.51],[10033,1,14.72],[20014,1,16.89],[20013,1,19.27],[20015,1,21.33],[30010,1,23.33],[30016,1,25.12],[30021,1,27.23],[40011,1,29.41],[40012,1,31.73],[40013,1,33.83]]</v>
+        <v>[[90037,1],[90038,1],[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H64">
-        <v>0.64</v>
+        <v>1.28</v>
       </c>
       <c r="I64">
-        <v>0.69</v>
+        <v>1.38</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -2279,13 +2272,13 @@
         <v>0</v>
       </c>
       <c r="G65" t="str">
-        <v>[[10033,1,0],[10014,1,1.69],[10015,1,3.36],[10019,1,5.15],[20014,1,6.76],[20013,1,8.83],[30021,1,10.77],[30010,1,12.57],[40011,1,14.72],[40012,1,16.39]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H65">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I65">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -2308,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="G66" t="str">
-        <v>[[10033,1,0],[10014,1,2.2],[10015,1,4.33],[10019,1,6.59],[10022,1,8.96],[20014,1,11.2],[20013,1,12.81],[30021,1,14.74],[30010,1,17.13],[40011,1,18.8],[40012,1,21.11]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H66">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I66">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -2337,13 +2330,13 @@
         <v>0</v>
       </c>
       <c r="G67" t="str">
-        <v>[[10033,1,0],[10014,1,2.05],[10015,1,4.1],[10019,1,6.15],[10022,1,8.26],[20014,1,10.47],[20013,1,12.27],[20015,1,14.13],[30021,1,16.32],[30010,1,18.53],[40011,1,20.29],[40012,1,22.64]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H67">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I67">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -2366,13 +2359,13 @@
         <v>0</v>
       </c>
       <c r="G68" t="str">
-        <v>[[10033,1,0],[10014,1,1.87],[10015,1,3.69],[10019,1,5.99],[10022,1,7.6],[20014,1,9.29],[20013,1,11.39],[20015,1,13],[30021,1,15.14],[30010,1,17.45],[40011,1,19.32],[40012,1,21.41]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H68">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I68">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -2395,13 +2388,13 @@
         <v>0</v>
       </c>
       <c r="G69" t="str">
-        <v>[[10033,1,0],[10014,1,2.3],[10015,1,4.1],[10019,1,5.81],[10022,1,8.18],[20014,1,10.5],[20013,1,12.15],[20015,1,13.95],[30021,1,15.89],[30010,1,18.15],[40011,1,20.37],[40012,1,22.56]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H69">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I69">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -2424,13 +2417,13 @@
         <v>0</v>
       </c>
       <c r="G70" t="str">
-        <v>[[10033,1,0],[10014,1,2.34],[10015,1,4.03],[10019,1,6.03],[10022,1,7.84],[20014,1,9.81],[20013,1,11.58],[20015,1,13.75],[30021,1,15.53],[30010,1,17.49],[40011,1,19.35],[40012,1,21.63]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H70">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I70">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -2453,13 +2446,13 @@
         <v>0</v>
       </c>
       <c r="G71" t="str">
-        <v>[[10033,1,0],[10014,1,1.95],[10015,1,3.94],[10019,1,5.6],[10022,1,7.35],[20014,1,9.06],[20013,1,10.91],[20015,1,13.21],[30021,1,15.49],[30010,1,17.64],[40011,1,19.46],[40012,1,21.83]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H71">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I71">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -2482,13 +2475,13 @@
         <v>0</v>
       </c>
       <c r="G72" t="str">
-        <v>[[10033,1,0],[10014,1,2.02],[10015,1,3.75],[10019,1,5.37],[10022,1,7.1],[20014,1,9.37],[20013,1,11.58],[20015,1,13.46],[30021,1,15.15],[30010,1,17.14],[40011,1,19.39],[40012,1,21.21]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H72">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I72">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -2511,13 +2504,13 @@
         <v>0</v>
       </c>
       <c r="G73" t="str">
-        <v>[[10033,1,0],[10014,1,1.6],[10015,1,3.66],[10019,1,5.66],[10022,1,7.5],[10024,1,9.81],[20014,1,11.81],[20013,1,13.61],[20015,1,15.88],[30021,1,17.7],[30010,1,20.07],[30016,1,22.08],[40011,1,24.41],[40012,1,26.1]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H73">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="I73">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -2540,13 +2533,13 @@
         <v>1</v>
       </c>
       <c r="G74" t="str">
-        <v>[[90037,1,0],[90038,1,2.58],[10033,1,4.97],[10014,1,6.61],[10015,1,8.46],[10019,1,10.11],[10022,1,12.4],[10024,1,14.66],[10034,1,16.81],[20014,1,18.89],[20013,1,20.63],[20015,1,22.37],[20018,1,24.65],[30021,1,26.84],[30010,1,29.14],[30016,1,31.2],[40011,1,33.51],[40012,1,35.11],[40020,1,36.95]]</v>
+        <v>[[90037,1],[90038,1],[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H74">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="I74">
-        <v>0.76</v>
+        <v>1.52</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -2569,13 +2562,13 @@
         <v>0</v>
       </c>
       <c r="G75" t="str">
-        <v>[[10033,1,0],[10034,1,1.71],[10022,1,3.99],[10014,1,5.73],[20014,1,7.54],[20013,1,9.66],[30021,1,11.84],[30010,1,14.16],[40020,1,16.51],[40011,1,18.86]]</v>
+        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H75">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I75">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -2598,13 +2591,13 @@
         <v>0</v>
       </c>
       <c r="G76" t="str">
-        <v>[[10033,1,0],[10034,1,1.68],[10022,1,3.75],[10014,1,5.79],[10030,1,7.91],[20014,1,9.55],[20013,1,11.67],[20015,1,13.54],[30021,1,15.39],[30010,1,17.57],[30016,1,19.95],[40020,1,21.9],[40011,1,23.93]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H76">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I76">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -2627,13 +2620,13 @@
         <v>0</v>
       </c>
       <c r="G77" t="str">
-        <v>[[10033,1,0],[10034,1,2.22],[10030,1,4.48],[10022,1,6.09],[10014,1,8.25],[20014,1,10.14],[20013,1,12.11],[20015,1,14.39],[30021,1,16.74],[30010,1,18.54],[30016,1,20.14],[40020,1,22.52],[40011,1,24.52]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H77">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I77">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -2656,13 +2649,13 @@
         <v>0</v>
       </c>
       <c r="G78" t="str">
-        <v>[[10033,1,0],[10034,1,1.69],[10030,1,3.79],[10022,1,6.01],[10014,1,7.94],[20014,1,10.27],[20013,1,12.02],[20015,1,14.02],[30021,1,16.37],[30010,1,18.04],[30016,1,20.26],[40020,1,22.16],[40011,1,24.31]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H78">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I78">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -2685,13 +2678,13 @@
         <v>0</v>
       </c>
       <c r="G79" t="str">
-        <v>[[10033,1,0],[10034,1,2.07],[10030,1,4.05],[10022,1,6.04],[10014,1,7.73],[20014,1,9.44],[20013,1,11.81],[20015,1,13.63],[30021,1,15.85],[30010,1,17.63],[30016,1,20.03],[40020,1,22.07],[40011,1,23.68]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H79">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I79">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -2714,13 +2707,13 @@
         <v>0</v>
       </c>
       <c r="G80" t="str">
-        <v>[[10033,1,0],[10034,1,2.01],[10030,1,3.75],[10022,1,6.12],[10014,1,8.37],[20014,1,10.39],[20013,1,12.57],[20015,1,14.93],[30021,1,16.78],[30010,1,18.63],[30016,1,20.33],[40020,1,22.65],[40011,1,25.02]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H80">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I80">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -2743,13 +2736,13 @@
         <v>0</v>
       </c>
       <c r="G81" t="str">
-        <v>[[10033,1,0],[10034,1,1.74],[10030,1,3.56],[10022,1,5.31],[10014,1,7.48],[20014,1,9.58],[20013,1,11.53],[20015,1,13.88],[30021,1,16.19],[30010,1,18.28],[30016,1,20.16],[40020,1,22.54],[40011,1,24.5]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H81">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I81">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J81">
         <v>1</v>
@@ -2772,13 +2765,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="str">
-        <v>[[10033,1,0],[10034,1,2.15],[10030,1,4.52],[10022,1,6.55],[10014,1,8.18],[20014,1,9.92],[20013,1,12.11],[20015,1,14.17],[30021,1,16.38],[30010,1,18.38],[30016,1,20.6],[40020,1,22.39],[40011,1,24.26]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H82">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I82">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J82">
         <v>1</v>
@@ -2801,13 +2794,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="str">
-        <v>[[10033,1,0],[10034,1,2.31],[10030,1,4.37],[10022,1,6.03],[10014,1,7.65],[10015,1,9.85],[20014,1,11.63],[20013,1,13.59],[20015,1,15.94],[30021,1,18.04],[30010,1,20.21],[30016,1,22.36],[40020,1,24.18],[40011,1,25.8],[40012,1,27.95]]</v>
+        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H83">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="I83">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="J83">
         <v>1</v>
@@ -2830,13 +2823,13 @@
         <v>1</v>
       </c>
       <c r="G84" t="str">
-        <v>[[90037,1,0],[90038,1,2.75],[10034,1,5.24],[10033,1,7.26],[10030,1,9.03],[10014,1,10.73],[10022,1,12.57],[10015,1,14.46],[10035,1,16.23],[20014,1,18.42],[20013,1,20.26],[20015,1,22.63],[20028,1,24.9],[30021,1,26.92],[30010,1,28.73],[30016,1,30.93],[30020,1,33.02],[40020,1,35.41],[40011,1,37.69],[40012,1,39.31]]</v>
+        <v>[[90037,1],[90038,1],[10014,1],[10022,1],[10017,1],[20014,1],[30014,1],[40014,1]]</v>
       </c>
       <c r="H84">
-        <v>0.77</v>
+        <v>1.54</v>
       </c>
       <c r="I84">
-        <v>0.84</v>
+        <v>1.67</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -2859,13 +2852,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="str">
-        <v>[[10033,1,0],[10034,1,2.13],[10030,1,4.01],[10035,1,6.1],[20028,1,7.96],[20029,1,10.23],[30021,1,12.4],[30020,1,14.49],[40020,2,16.24]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H85">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I85">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -2888,13 +2881,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="str">
-        <v>[[10033,1,0],[10034,1,2.12],[10030,1,4.13],[10035,1,5.98],[10028,1,7.96],[20028,1,9.95],[20029,1,11.73],[30021,1,13.64],[30020,1,15.48],[40020,1,17.52],[40023,1,19.31]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H86">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I86">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -2917,13 +2910,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="str">
-        <v>[[10033,1,0],[10034,1,1.95],[10030,1,4.18],[10035,1,6.49],[10028,1,8.48],[20028,1,10.25],[20029,1,12.26],[30021,1,14.09],[30020,1,16.15],[40020,1,17.82],[40023,1,19.55]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H87">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I87">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J87">
         <v>1</v>
@@ -2946,13 +2939,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="str">
-        <v>[[10033,1,0],[10034,1,2.27],[10030,1,4.28],[10035,1,5.89],[10028,1,7.62],[20028,1,9.86],[20029,1,11.78],[30021,1,13.51],[30020,1,15.74],[40020,1,18.07],[40023,1,20.18]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H88">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I88">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J88">
         <v>1</v>
@@ -2975,13 +2968,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="str">
-        <v>[[10033,1,0],[10034,1,2.3],[10030,1,4.43],[10035,1,6.7],[10028,1,8.45],[20028,1,10.13],[20029,1,12.22],[30021,1,13.84],[30020,1,15.6],[40020,1,17.85],[40023,1,19.9]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H89">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I89">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -3004,13 +2997,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="str">
-        <v>[[10033,1,0],[10034,1,2.4],[10030,1,4.67],[10035,1,6.57],[10028,1,8.31],[20028,1,10.65],[20029,1,12.56],[30021,1,14.4],[30020,1,16.12],[40020,1,18.46],[40023,1,20.66]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H90">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I90">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -3033,13 +3026,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="str">
-        <v>[[10033,1,0],[10034,1,1.78],[10030,1,3.49],[10035,1,5.87],[10028,1,7.85],[20028,1,9.64],[20029,1,11.34],[30021,1,13.27],[30020,1,14.91],[40020,1,16.6],[40023,1,18.43]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H91">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I91">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -3062,13 +3055,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="str">
-        <v>[[10033,1,0],[10034,1,1.88],[10030,1,3.5],[10035,1,5.8],[10028,1,7.55],[20028,1,9.68],[20029,1,11.44],[30021,1,13.75],[30020,1,15.98],[40020,1,17.69],[40023,1,20.08]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H92">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I92">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J92">
         <v>1</v>
@@ -3091,13 +3084,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="str">
-        <v>[[10033,1,0],[10034,1,1.95],[10030,1,4.08],[10035,1,6.43],[10028,1,8.38],[20028,1,10],[20029,1,11.74],[30021,1,13.5],[30020,1,15.15],[30018,1,16.94],[40020,1,18.81],[40023,1,20.72]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H93">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="I93">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="J93">
         <v>1</v>
@@ -3120,13 +3113,13 @@
         <v>1</v>
       </c>
       <c r="G94" t="str">
-        <v>[[90039,1,0],[90040,1,2.35],[10033,1,4.83],[10034,1,6.67],[10030,1,8.76],[10035,1,10.67],[10028,1,12.28],[10048,1,14.64],[10032,1,16.83],[20028,1,18.51],[20029,1,20.66],[20034,1,22.76],[30021,1,24.49],[30020,1,26.82],[30018,1,29.1],[40020,1,31.48],[40023,1,33.48],[40017,1,35.39]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H94">
-        <v>0.85</v>
+        <v>1.7</v>
       </c>
       <c r="I94">
-        <v>0.92</v>
+        <v>1.84</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -3149,13 +3142,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="str">
-        <v>[[10048,1,0],[10033,1,2.12],[10034,1,4.17],[10030,1,6.48],[20028,1,8.53],[20029,1,10.91],[30021,1,13.11],[30020,1,14.76],[40020,1,16.93],[40023,1,19.18]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H95">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I95">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J95">
         <v>1</v>
@@ -3178,13 +3171,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="str">
-        <v>[[10048,1,0],[10033,1,1.82],[10034,1,3.5],[10030,1,5.6],[10037,1,7.75],[20028,1,9.95],[20029,1,11.75],[30021,1,13.39],[30020,1,15.07],[30018,1,16.91],[40020,1,18.77],[40023,1,21.05]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H96">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I96">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -3207,13 +3200,13 @@
         <v>0</v>
       </c>
       <c r="G97" t="str">
-        <v>[[10048,1,0],[10037,1,1.81],[10033,1,3.69],[10034,1,5.84],[10030,1,8.03],[20028,1,9.94],[20029,1,11.88],[30021,1,14.17],[30020,1,15.89],[30018,1,18.08],[40020,1,19.79],[40023,1,22.09]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H97">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I97">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J97">
         <v>1</v>
@@ -3236,13 +3229,13 @@
         <v>0</v>
       </c>
       <c r="G98" t="str">
-        <v>[[10048,1,0],[10037,1,2.23],[10033,1,4.3],[10034,1,6.42],[10030,1,8.26],[20028,1,10.11],[20029,1,11.72],[30021,1,13.37],[30020,1,15.65],[30018,1,17.54],[40020,1,19.74],[40023,1,22]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H98">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I98">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J98">
         <v>1</v>
@@ -3265,13 +3258,13 @@
         <v>0</v>
       </c>
       <c r="G99" t="str">
-        <v>[[10048,1,0],[10037,1,2.05],[10033,1,4.33],[10034,1,6.38],[10030,1,8.65],[20028,1,10.69],[20029,1,12.43],[30021,1,14.12],[30020,1,16.04],[30018,1,17.93],[40020,1,19.9],[40023,1,22.22]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H99">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I99">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -3294,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="G100" t="str">
-        <v>[[10048,1,0],[10037,1,1.71],[10033,1,3.69],[10034,1,5.95],[10030,1,8.28],[20028,1,9.97],[20029,1,12.06],[30021,1,13.9],[30020,1,15.59],[30018,1,17.31],[40020,1,19.56],[40023,1,21.49]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H100">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I100">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -3323,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="G101" t="str">
-        <v>[[10048,1,0],[10037,1,1.78],[10033,1,4.02],[10034,1,5.81],[10030,1,7.99],[20028,1,10],[20029,1,11.78],[30021,1,13.68],[30020,1,15.8],[30018,1,17.46],[40020,1,19.72],[40023,1,21.91]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H101">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I101">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -3352,13 +3345,13 @@
         <v>0</v>
       </c>
       <c r="G102" t="str">
-        <v>[[10048,1,0],[10037,1,1.7],[10033,1,3.81],[10034,1,5.88],[10030,1,7.95],[20028,1,10.25],[20029,1,12.38],[30021,1,14.03],[30020,1,16.07],[30018,1,18.27],[40020,1,20.52],[40023,1,22.18]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H102">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I102">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -3381,13 +3374,13 @@
         <v>0</v>
       </c>
       <c r="G103" t="str">
-        <v>[[10048,1,0],[10037,1,1.77],[10033,1,3.6],[10034,1,5.77],[10030,1,7.72],[10043,1,9.53],[20028,1,11.83],[20029,1,13.9],[20034,1,16.23],[30021,1,18.61],[30020,1,20.32],[30018,1,22.34],[40020,1,24.44],[40023,1,26.61],[40017,1,28.88]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H103">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="I103">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="J103">
         <v>1</v>
@@ -3410,13 +3403,13 @@
         <v>1</v>
       </c>
       <c r="G104" t="str">
-        <v>[[90039,1,0],[90040,1,2.79],[10048,1,5.26],[10037,1,7.52],[10043,1,9.81],[10034,1,12.13],[10033,1,14.34],[10030,1,16.04],[10041,1,17.91],[10042,1,19.97],[20028,1,22.01],[20034,1,23.85],[20029,1,25.84],[20032,1,27.81],[30021,1,29.43],[30020,1,31.44],[30018,1,33.63],[30029,1,35.42],[30019,1,37.47],[40020,1,39.46],[40017,1,41.69],[40023,1,44.08],[40021,1,46.35]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H104">
-        <v>1.09</v>
+        <v>2.18</v>
       </c>
       <c r="I104">
-        <v>1.24</v>
+        <v>2.49</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -3439,13 +3432,13 @@
         <v>0</v>
       </c>
       <c r="G105" t="str">
-        <v>[[10048,1,0],[10037,1,2.16],[10043,1,4.37],[10041,1,6.5],[20028,1,8.17],[20034,1,10.41],[30029,1,12.4],[30021,1,14.41],[40020,1,16.43],[40017,1,18.5]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H105">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I105">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J105">
         <v>1</v>
@@ -3468,13 +3461,13 @@
         <v>0</v>
       </c>
       <c r="G106" t="str">
-        <v>[[10048,1,0],[10037,1,1.98],[10043,1,4.23],[10041,1,5.85],[10042,1,7.71],[20028,1,9.78],[20034,1,11.97],[20029,1,13.7],[30029,1,15.66],[30021,1,17.53],[30020,1,19.28],[40020,1,20.94],[40017,1,22.85],[40023,1,24.79]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H106">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I106">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J106">
         <v>1</v>
@@ -3497,13 +3490,13 @@
         <v>0</v>
       </c>
       <c r="G107" t="str">
-        <v>[[10048,1,0],[10037,1,2.09],[10043,1,3.7],[10041,1,6.03],[10042,1,8.06],[20028,1,10.44],[20034,1,12.49],[20029,1,14.24],[30029,1,16.54],[30021,1,18.6],[30020,1,20.69],[40020,1,22.53],[40017,1,24.9],[40023,1,27.14]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H107">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I107">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J107">
         <v>1</v>
@@ -3526,13 +3519,13 @@
         <v>0</v>
       </c>
       <c r="G108" t="str">
-        <v>[[10048,1,0],[10037,1,1.9],[10043,1,3.98],[10041,1,6.15],[10042,1,8.01],[20028,1,9.69],[20034,1,11.45],[20029,1,13.68],[30029,1,15.95],[30021,1,18.26],[30020,1,19.99],[40020,1,21.6],[40017,1,23.28],[40023,1,25.55]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H108">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I108">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -3555,13 +3548,13 @@
         <v>0</v>
       </c>
       <c r="G109" t="str">
-        <v>[[10048,1,0],[10037,1,1.95],[10043,1,4.34],[10041,1,6.54],[10042,1,8.68],[20028,1,10.87],[20034,1,12.74],[20029,1,14.45],[30029,1,16.3],[30021,1,18.14],[30020,1,19.96],[40020,1,21.89],[40017,1,23.56],[40023,1,25.43]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H109">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I109">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J109">
         <v>1</v>
@@ -3584,13 +3577,13 @@
         <v>0</v>
       </c>
       <c r="G110" t="str">
-        <v>[[10048,1,0],[10037,1,2.27],[10043,1,4.55],[10041,1,6.29],[10042,1,8.44],[20028,1,10.4],[20034,1,12.56],[20029,1,14.85],[30029,1,17.04],[30021,1,19.15],[30020,1,20.81],[40020,1,22.99],[40017,1,24.92],[40023,1,26.99]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H110">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I110">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J110">
         <v>1</v>
@@ -3613,13 +3606,13 @@
         <v>0</v>
       </c>
       <c r="G111" t="str">
-        <v>[[10048,1,0],[10037,1,2.09],[10043,1,3.83],[10041,1,5.69],[10042,1,7.45],[20028,1,9.67],[20034,1,11.36],[20029,1,13.24],[30029,1,15.55],[30021,1,17.7],[30020,1,19.8],[40020,1,21.79],[40017,1,23.54],[40023,1,25.4]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H111">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I111">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J111">
         <v>1</v>
@@ -3642,13 +3635,13 @@
         <v>0</v>
       </c>
       <c r="G112" t="str">
-        <v>[[10048,1,0],[10037,1,1.68],[10043,1,4.04],[10041,1,6.33],[10042,1,8.33],[20028,1,10.54],[20034,1,12.71],[20029,1,14.96],[30029,1,16.61],[30021,1,18.34],[30020,1,20.7],[40020,1,22.88],[40017,1,25.06],[40023,1,27.2]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H112">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I112">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J112">
         <v>1</v>
@@ -3671,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="G113" t="str">
-        <v>[[10048,1,0],[10037,1,1.84],[10043,1,3.54],[10041,1,5.14],[10042,1,7.15],[10034,1,9.14],[20028,1,11.45],[20034,1,13.4],[20029,1,15.17],[30029,1,17.19],[30021,1,19.34],[30020,1,21.72],[40020,1,23.89],[40017,1,26.18],[40023,1,28.34]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H113">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="I113">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J113">
         <v>1</v>
@@ -3700,13 +3693,13 @@
         <v>1</v>
       </c>
       <c r="G114" t="str">
-        <v>[[90039,1,0],[90040,1,2.78],[10048,1,5.59],[10037,1,7.27],[10043,1,9.2],[10042,1,10.86],[10041,1,12.64],[10034,1,14.39],[10038,1,16.18],[10033,1,18.28],[20028,1,20.37],[20029,1,22.75],[20034,1,25.13],[20032,1,26.76],[30029,1,29.09],[30021,1,31.46],[30020,1,33.27],[30028,1,35.24],[40020,1,37.01],[40017,1,38.73],[40023,1,41.11],[40022,1,42.75]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H114">
-        <v>1.03</v>
+        <v>2.05</v>
       </c>
       <c r="I114">
-        <v>1.11</v>
+        <v>2.23</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -3729,13 +3722,13 @@
         <v>0</v>
       </c>
       <c r="G115" t="str">
-        <v>[[10048,1,0],[10037,1,1.76],[10043,1,3.47],[10041,1,5.12],[10042,1,7.29],[20028,1,9.49],[20029,1,11.52],[20034,1,13.85],[30029,1,15.96],[30028,1,18.14],[40020,1,20.13],[40017,1,22.03],[40023,1,23.91]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H115">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I115">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J115">
         <v>1</v>
@@ -3758,13 +3751,13 @@
         <v>0</v>
       </c>
       <c r="G116" t="str">
-        <v>[[10048,1,0],[10037,1,2.24],[10043,1,3.86],[10041,1,6.22],[10042,1,8.22],[10038,1,10.42],[20028,1,12.54],[20029,1,14.39],[20034,1,16.12],[30029,1,18.1],[30028,1,19.72],[30021,1,21.75],[40020,1,23.55],[40017,1,25.19],[40023,1,26.91]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H116">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I116">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J116">
         <v>1</v>
@@ -3787,13 +3780,13 @@
         <v>0</v>
       </c>
       <c r="G117" t="str">
-        <v>[[10048,1,0],[10037,1,2.05],[10043,1,4],[10041,1,5.74],[10042,1,7.72],[10038,1,9.82],[20028,1,11.86],[20029,1,14.08],[20034,1,16.11],[30029,1,18.1],[30028,1,20.07],[30021,1,22.02],[40020,1,23.92],[40017,1,25.9],[40023,1,27.93]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H117">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I117">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J117">
         <v>1</v>
@@ -3816,13 +3809,13 @@
         <v>0</v>
       </c>
       <c r="G118" t="str">
-        <v>[[10048,1,0],[10037,1,2.38],[10043,1,4.41],[10041,1,6.28],[10042,1,7.99],[10038,1,10.2],[20028,1,11.96],[20029,1,13.98],[20034,1,16.33],[30029,1,18.41],[30028,1,20.36],[30021,1,22.21],[40020,1,23.84],[40017,1,25.44],[40023,1,27.06]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H118">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I118">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J118">
         <v>1</v>
@@ -3845,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="G119" t="str">
-        <v>[[10048,1,0],[10037,1,1.96],[10043,1,3.6],[10041,1,5.93],[10042,1,8.29],[10038,1,9.89],[20028,1,12.05],[20029,1,14.15],[20034,1,16.33],[30029,1,18],[30028,1,20.18],[30021,1,22.15],[40020,1,24.49],[40017,1,26.77],[40023,1,28.52]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H119">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I119">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J119">
         <v>1</v>
@@ -3874,13 +3867,13 @@
         <v>0</v>
       </c>
       <c r="G120" t="str">
-        <v>[[10048,1,0],[10037,1,1.69],[10043,1,3.44],[10041,1,5.66],[10042,1,7.97],[10038,1,9.69],[20028,1,11.65],[20029,1,13.26],[20034,1,15.45],[30029,1,17.74],[30028,1,19.88],[30021,1,21.94],[40020,1,23.66],[40017,1,25.34],[40023,1,27.13]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H120">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I120">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J120">
         <v>1</v>
@@ -3903,13 +3896,13 @@
         <v>0</v>
       </c>
       <c r="G121" t="str">
-        <v>[[10048,1,0],[10037,1,2.32],[10043,1,4.39],[10041,1,6.42],[10042,1,8.64],[10038,1,10.24],[20028,1,12.23],[20029,1,14.23],[20034,1,16.49],[30029,1,18.24],[30028,1,20.45],[30021,1,22.22],[40020,1,24.48],[40017,1,26.42],[40023,1,28.54]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H121">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I121">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J121">
         <v>1</v>
@@ -3932,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G122" t="str">
-        <v>[[10048,1,0],[10037,1,2],[10043,1,4.32],[10041,1,6.33],[10042,1,7.94],[10038,1,10.04],[20028,1,11.9],[20029,1,13.69],[20034,1,15.62],[30029,1,17.49],[30028,1,19.24],[30021,1,20.87],[40020,1,22.82],[40017,1,24.67],[40023,1,26.34]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H122">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I122">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J122">
         <v>1</v>
@@ -3961,13 +3954,13 @@
         <v>0</v>
       </c>
       <c r="G123" t="str">
-        <v>[[10048,1,0],[10037,1,2.31],[10043,1,4.48],[10041,1,6.54],[10042,1,8.85],[10038,1,10.63],[10033,1,12.86],[20028,1,14.67],[20029,1,16.46],[20034,1,18.35],[20039,1,20.04],[30029,1,22.44],[30028,1,24.77],[30021,1,26.69],[30020,1,29.08],[40020,1,31.08],[40017,1,33.27],[40023,1,35.13]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H123">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="I123">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="J123">
         <v>1</v>
@@ -3990,13 +3983,13 @@
         <v>1</v>
       </c>
       <c r="G124" t="str">
-        <v>[[90039,1,0],[90040,1,2.43],[10048,1,4.82],[10037,1,6.9],[10043,1,8.86],[10042,1,10.5],[10038,1,12.41],[10041,1,14.53],[10033,1,16.75],[10040,1,18.58],[10034,1,20.67],[20039,1,22.45],[20028,1,24.31],[20034,1,26.57],[20029,1,28.51],[30029,1,30.17],[30028,1,32.56],[30021,1,34.2],[30020,1,36.18],[30018,1,37.94],[40020,1,39.62],[40017,1,41.67],[40023,1,43.81],[40025,1,45.66]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10045,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H124">
-        <v>1.13</v>
+        <v>2.26</v>
       </c>
       <c r="I124">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="J124">
         <v>1</v>
@@ -4019,13 +4012,13 @@
         <v>0</v>
       </c>
       <c r="G125" t="str">
-        <v>[[10048,1,0],[10037,1,1.68],[10043,1,3.56],[10042,1,5.83],[10040,1,7.51],[10033,1,9.71],[20039,1,11.54],[20028,1,13.78],[20029,1,16.14],[30029,1,18.35],[30028,1,20.3],[30021,1,22.25],[40025,1,24.01],[40020,1,25.78],[40017,1,27.81]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H125">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I125">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J125">
         <v>1</v>
@@ -4048,13 +4041,13 @@
         <v>0</v>
       </c>
       <c r="G126" t="str">
-        <v>[[10048,1,0],[10037,1,1.6],[10043,1,3.74],[10042,1,6.04],[10040,1,8.14],[10033,1,10.21],[10041,1,12.6],[20039,1,14.63],[20028,1,16.46],[20029,1,18.85],[20034,1,20.52],[30029,1,22.83],[30028,1,25.02],[30021,1,27.37],[30020,1,29.06],[40025,1,30.94],[40020,1,32.72],[40017,1,34.38]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H126">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I126">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J126">
         <v>1</v>
@@ -4077,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="G127" t="str">
-        <v>[[10048,1,0],[10037,1,2.02],[10043,1,4],[10042,1,5.64],[10040,1,8.03],[10041,1,10.21],[10033,1,12.31],[20039,1,14.03],[20028,1,16.42],[20029,1,18.16],[20034,1,20.29],[30029,1,22.41],[30028,1,24.14],[30021,1,25.94],[30020,1,27.63],[40025,1,30.01],[40020,1,32],[40017,1,33.95]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H127">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I127">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J127">
         <v>1</v>
@@ -4106,13 +4099,13 @@
         <v>0</v>
       </c>
       <c r="G128" t="str">
-        <v>[[10048,1,0],[10037,1,1.87],[10043,1,3.66],[10042,1,5.75],[10040,1,7.76],[10041,1,9.63],[10033,1,11.65],[20039,1,13.74],[20028,1,15.51],[20029,1,17.28],[20034,1,19.23],[30029,1,21.2],[30028,1,23.21],[30021,1,24.94],[30020,1,27.21],[40025,1,29.19],[40020,1,31.28],[40017,1,33.37]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H128">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I128">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J128">
         <v>1</v>
@@ -4135,13 +4128,13 @@
         <v>0</v>
       </c>
       <c r="G129" t="str">
-        <v>[[10048,1,0],[10037,1,1.66],[10043,1,3.35],[10042,1,5.06],[10040,1,7.42],[10041,1,9.63],[10033,1,11.94],[20039,1,13.81],[20028,1,15.64],[20029,1,17.89],[20034,1,19.61],[30029,1,21.78],[30028,1,23.41],[30021,1,25.26],[30020,1,27.27],[40025,1,29.59],[40020,1,31.94],[40017,1,33.59]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H129">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I129">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J129">
         <v>1</v>
@@ -4164,13 +4157,13 @@
         <v>0</v>
       </c>
       <c r="G130" t="str">
-        <v>[[10048,1,0],[10037,1,2.09],[10043,1,4.45],[10042,1,6.8],[10040,1,9.07],[10041,1,11.28],[10033,1,13.54],[20039,1,15.83],[20028,1,17.5],[20029,1,19.49],[20034,1,21.26],[30029,1,23.47],[30028,1,25.3],[30021,1,27.08],[30020,1,29.06],[40025,1,31.46],[40020,1,33.29],[40017,1,35.03]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H130">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I130">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J130">
         <v>1</v>
@@ -4193,13 +4186,13 @@
         <v>0</v>
       </c>
       <c r="G131" t="str">
-        <v>[[10048,1,0],[10037,1,1.97],[10043,1,3.91],[10042,1,6.06],[10040,1,8.4],[10041,1,10.51],[10033,1,12.88],[20039,1,14.75],[20028,1,16.69],[20029,1,18.84],[20034,1,20.56],[30029,1,22.8],[30028,1,25.15],[30021,1,27.25],[30020,1,29.03],[40025,1,31.43],[40020,1,33.43],[40017,1,35.38]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H131">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I131">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J131">
         <v>1</v>
@@ -4222,13 +4215,13 @@
         <v>0</v>
       </c>
       <c r="G132" t="str">
-        <v>[[10048,1,0],[10037,1,2.16],[10043,1,4.45],[10042,1,6.05],[10040,1,7.87],[10041,1,9.53],[10033,1,11.51],[20039,1,13.53],[20028,1,15.4],[20029,1,17.36],[20034,1,19.74],[30029,1,21.96],[30028,1,23.93],[30021,1,26.08],[30020,1,28.33],[40025,1,30.53],[40020,1,32.47],[40017,1,34.74]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H132">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I132">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J132">
         <v>1</v>
@@ -4251,13 +4244,13 @@
         <v>0</v>
       </c>
       <c r="G133" t="str">
-        <v>[[10048,1,0],[10037,1,1.71],[10043,1,3.77],[10042,1,5.85],[10040,1,7.55],[10041,1,9.75],[10033,1,12.06],[10038,1,14.01],[20039,1,16.06],[20028,1,18.34],[20029,1,20.55],[20034,1,22.19],[30029,1,24.37],[30028,1,26.01],[30021,1,28.13],[30020,1,29.91],[40025,1,32.06],[40020,1,33.7],[40017,1,35.81],[40023,1,37.6]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H133">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="I133">
-        <v>0.94</v>
+        <v>1.88</v>
       </c>
       <c r="J133">
         <v>1</v>
@@ -4280,13 +4273,13 @@
         <v>1</v>
       </c>
       <c r="G134" t="str">
-        <v>[[90039,1,0],[90040,1,2.33],[10048,1,4.69],[10037,1,6.79],[10043,1,8.94],[10042,1,11.16],[10041,1,12.87],[10038,1,14.67],[10040,1,16.61],[10033,1,18.51],[10039,1,20.27],[10034,1,22.55],[20039,1,24.37],[20028,1,25.98],[20029,1,27.65],[20034,1,29.85],[20032,1,31.92],[30029,1,34.25],[30028,1,35.88],[30021,1,38.05],[30020,1,40.28],[30030,1,42.08],[40025,1,44.23],[40020,1,46.51],[40023,1,48.11],[40017,1,50.34],[40021,1,52.55]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H134">
-        <v>1.24</v>
+        <v>2.49</v>
       </c>
       <c r="I134">
-        <v>1.35</v>
+        <v>2.69</v>
       </c>
       <c r="J134">
         <v>1</v>
@@ -4309,13 +4302,13 @@
         <v>0</v>
       </c>
       <c r="G135" t="str">
-        <v>[[10048,1,0],[10037,1,1.83],[10043,1,4.14],[10042,1,6.03],[10041,1,8.39],[10038,1,10.35],[20039,1,12.64],[20028,1,14.65],[20034,1,16.4],[30029,1,18.35],[30028,1,20.46],[30030,1,22.32],[40025,1,24.48],[40020,1,26.12],[40017,1,27.76]]</v>
+        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H135">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I135">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J135">
         <v>1</v>
@@ -4338,13 +4331,13 @@
         <v>0</v>
       </c>
       <c r="G136" t="str">
-        <v>[[10048,1,0],[10037,1,1.73],[10043,1,3.44],[10042,1,5.1],[10041,1,7.36],[10038,1,9.33],[10040,1,10.97],[10033,1,13.29],[20039,1,15.68],[20028,1,17.87],[20034,1,20.27],[20048,1,22.26],[30029,1,24.19],[30028,1,26.59],[30030,1,28.28],[30021,1,30.36],[40025,1,32],[40020,1,34.27],[40017,1,36],[40023,1,37.91]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H136">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I136">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J136">
         <v>1</v>
@@ -4367,13 +4360,13 @@
         <v>0</v>
       </c>
       <c r="G137" t="str">
-        <v>[[10048,1,0],[10037,1,2.19],[10043,1,4.46],[10042,1,6.06],[10041,1,8.12],[10038,1,10.06],[10040,1,11.73],[10033,1,13.97],[20039,1,15.83],[20048,1,17.96],[20028,1,20.2],[20034,1,21.83],[30029,1,24.18],[30028,1,25.98],[30030,1,27.89],[30021,1,30.05],[40025,1,31.71],[40020,1,33.58],[40017,1,35.7],[40023,1,37.95]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H137">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I137">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J137">
         <v>1</v>
@@ -4396,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="G138" t="str">
-        <v>[[10048,1,0],[10037,1,1.93],[10043,1,4.01],[10042,1,5.66],[10041,1,7.37],[10038,1,9.5],[10040,1,11.53],[10033,1,13.57],[20039,1,15.21],[20048,1,16.96],[20028,1,18.85],[20034,1,20.93],[30029,1,22.92],[30028,1,24.93],[30030,1,27.16],[30021,1,29.06],[40025,1,31.28],[40020,1,33.06],[40017,1,35.17],[40023,1,37.24]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H138">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I138">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J138">
         <v>1</v>
@@ -4425,13 +4418,13 @@
         <v>0</v>
       </c>
       <c r="G139" t="str">
-        <v>[[10048,1,0],[10037,1,1.92],[10043,1,4.16],[10042,1,5.87],[10041,1,7.56],[10038,1,9.68],[10040,1,11.44],[10033,1,13.36],[20039,1,14.97],[20048,1,17.15],[20028,1,18.94],[20034,1,20.66],[30029,1,22.46],[30028,1,24.39],[30030,1,26.78],[30021,1,28.47],[40025,1,30.49],[40020,1,32.59],[40017,1,34.83],[40023,1,37.14]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H139">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I139">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J139">
         <v>1</v>
@@ -4454,13 +4447,13 @@
         <v>0</v>
       </c>
       <c r="G140" t="str">
-        <v>[[10048,1,0],[10037,1,1.9],[10043,1,3.95],[10042,1,6.15],[10041,1,7.76],[10038,1,9.84],[10040,1,11.56],[10033,1,13.71],[20039,1,15.65],[20048,1,17.67],[20028,1,19.54],[20034,1,21.33],[30029,1,23.6],[30028,1,25.71],[30030,1,27.72],[30021,1,29.54],[40025,1,31.79],[40020,1,33.94],[40017,1,35.88],[40023,1,37.94]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H140">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I140">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J140">
         <v>1</v>
@@ -4483,13 +4476,13 @@
         <v>0</v>
       </c>
       <c r="G141" t="str">
-        <v>[[10048,1,0],[10037,1,1.78],[10043,1,3.85],[10042,1,6.07],[10041,1,8.37],[10038,1,10.04],[10040,1,12.08],[10033,1,14.2],[20039,1,16.33],[20048,1,18.22],[20028,1,20.53],[20034,1,22.28],[30029,1,24.08],[30028,1,26.26],[30030,1,28.27],[30021,1,30.18],[40025,1,32.16],[40020,1,34.09],[40017,1,35.79],[40023,1,37.87]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H141">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I141">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J141">
         <v>1</v>
@@ -4512,13 +4505,13 @@
         <v>0</v>
       </c>
       <c r="G142" t="str">
-        <v>[[10048,1,0],[10037,1,2.01],[10043,1,3.92],[10042,1,5.65],[10041,1,7.95],[10038,1,10.26],[10040,1,12.35],[10033,1,14.09],[20039,1,15.86],[20048,1,17.88],[20028,1,20.03],[20034,1,21.89],[30029,1,24.13],[30028,1,25.89],[30030,1,27.5],[30021,1,29.12],[40025,1,30.82],[40020,1,33.08],[40017,1,34.87],[40023,1,36.48]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H142">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I142">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J142">
         <v>1</v>
@@ -4541,13 +4534,13 @@
         <v>0</v>
       </c>
       <c r="G143" t="str">
-        <v>[[10048,1,0],[10037,1,1.85],[10043,1,3.46],[10042,1,5.43],[10041,1,7.65],[10038,1,9.52],[10040,1,11.88],[10033,1,13.95],[10034,1,15.94],[20039,1,17.58],[20048,1,19.68],[20028,1,21.54],[20034,1,23.65],[20029,1,25.7],[30029,1,27.38],[30028,1,29.42],[30030,1,31.66],[30021,1,33.3],[30020,1,35.44],[40025,1,37.17],[40020,1,39.35],[40017,1,41.63],[40023,1,43.62]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H143">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="I143">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="J143">
         <v>1</v>
@@ -4570,13 +4563,13 @@
         <v>1</v>
       </c>
       <c r="G144" t="str">
-        <v>[[90039,1,0],[90040,1,2.9],[10048,1,5.86],[10037,1,7.56],[10043,1,9.81],[10042,1,11.95],[10038,1,13.8],[10041,1,15.72],[10040,1,18.06],[10034,1,20.45],[10033,1,22.69],[10039,1,25.05],[10045,1,27.18],[20039,1,29.58],[20048,1,31.9],[20028,1,34.29],[20034,1,36.52],[20029,1,38.65],[20032,1,40.88],[30029,1,43.18],[30028,1,45.18],[30030,1,47],[30021,1,48.79],[30020,1,51.11],[30025,1,53.14],[40025,1,55.49],[40020,1,57.62],[40017,1,59.8],[40023,1,61.55],[40030,1,63.73]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[10027,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H144">
-        <v>1.37</v>
+        <v>2.73</v>
       </c>
       <c r="I144">
-        <v>1.48</v>
+        <v>2.96</v>
       </c>
       <c r="J144">
         <v>1</v>
@@ -4599,13 +4592,13 @@
         <v>0</v>
       </c>
       <c r="G145" t="str">
-        <v>[[10048,1,0],[10037,1,2.2],[10043,1,4.38],[10042,1,6.68],[10041,1,8.41],[10038,1,10.4],[10040,1,12.49],[20039,1,14.42],[20048,1,16.79],[20028,1,18.79],[20029,1,20.7],[30029,1,23.01],[30028,1,24.63],[30025,1,26.24],[30021,1,27.93],[40025,1,29.62],[40030,1,31.86],[40020,1,33.89]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H145">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I145">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J145">
         <v>1</v>
@@ -4628,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="G146" t="str">
-        <v>[[10048,1,0],[10037,1,2.06],[10043,1,4.05],[10042,1,6.39],[10041,1,8.04],[10038,1,9.91],[10040,1,12],[10039,1,14.03],[10034,1,15.69],[20039,1,18.04],[20048,1,19.65],[20028,1,21.91],[20029,1,23.6],[20034,1,25.49],[30029,1,27.78],[30028,1,29.65],[30025,1,31.33],[30021,1,33.56],[30020,1,35.51],[40025,1,37.48],[40030,1,39.54],[40020,1,41.42],[40017,1,43.18]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H146">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I146">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J146">
         <v>1</v>
@@ -4657,13 +4650,13 @@
         <v>0</v>
       </c>
       <c r="G147" t="str">
-        <v>[[10048,1,0],[10037,1,1.7],[10043,1,3.79],[10042,1,5.63],[10041,1,7.77],[10038,1,9.65],[10040,1,11.26],[10039,1,13.31],[10034,1,15.55],[20039,1,17.84],[20048,1,19.8],[20028,1,21.6],[20029,1,23.82],[20034,1,25.71],[30029,1,27.96],[30028,1,30.25],[30025,1,31.97],[30021,1,33.74],[30020,1,35.94],[40025,1,38.24],[40030,1,39.92],[40020,1,41.82],[40017,1,44.1]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H147">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I147">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J147">
         <v>1</v>
@@ -4686,13 +4679,13 @@
         <v>0</v>
       </c>
       <c r="G148" t="str">
-        <v>[[10048,1,0],[10037,1,2.04],[10043,1,4.34],[10042,1,6.72],[10041,1,8.46],[10038,1,10.15],[10040,1,11.85],[10039,1,14.06],[10034,1,16.43],[20039,1,18.11],[20048,1,19.72],[20028,1,21.82],[20029,1,23.61],[20034,1,25.35],[30029,1,27.17],[30028,1,29.14],[30025,1,31.5],[30021,1,33.25],[30020,1,34.94],[40025,1,36.92],[40030,1,38.63],[40020,1,40.69],[40017,1,42.64]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H148">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I148">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J148">
         <v>1</v>
@@ -4715,13 +4708,13 @@
         <v>0</v>
       </c>
       <c r="G149" t="str">
-        <v>[[10048,1,0],[10037,1,2.35],[10043,1,4.53],[10042,1,6.44],[10041,1,8.4],[10038,1,10.16],[10040,1,12.26],[10039,1,14.45],[10034,1,16.41],[20039,1,18.21],[20048,1,20.22],[20028,1,22.44],[20029,1,24.76],[20034,1,26.7],[30029,1,29.01],[30028,1,30.85],[30025,1,32.57],[30021,1,34.24],[30020,1,36.32],[40025,1,38.51],[40030,1,40.72],[40020,1,42.56],[40017,1,44.6]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H149">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I149">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J149">
         <v>1</v>
@@ -4744,13 +4737,13 @@
         <v>0</v>
       </c>
       <c r="G150" t="str">
-        <v>[[10048,1,0],[10037,1,2.29],[10043,1,4.21],[10042,1,6.14],[10041,1,7.84],[10038,1,9.52],[10040,1,11.85],[10039,1,14.04],[10034,1,15.98],[20039,1,18.16],[20048,1,20.48],[20028,1,22.75],[20029,1,24.45],[20034,1,26.48],[30029,1,28.31],[30028,1,29.99],[30025,1,32.1],[30021,1,34.34],[30020,1,36.37],[40025,1,38.44],[40030,1,40.28],[40020,1,42.04],[40017,1,44.24]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H150">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I150">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J150">
         <v>1</v>
@@ -4773,13 +4766,13 @@
         <v>0</v>
       </c>
       <c r="G151" t="str">
-        <v>[[10048,1,0],[10037,1,2.29],[10043,1,4.26],[10042,1,6.42],[10041,1,8.73],[10038,1,10.5],[10040,1,12.83],[10039,1,15.17],[10034,1,17.38],[20039,1,19],[20048,1,20.98],[20028,1,22.64],[20029,1,24.99],[20034,1,26.84],[30029,1,28.54],[30028,1,30.36],[30025,1,32.39],[30021,1,34.32],[30020,1,36.53],[40025,1,38.43],[40030,1,40.69],[40020,1,42.95],[40017,1,45.2]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H151">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I151">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J151">
         <v>1</v>
@@ -4802,13 +4795,13 @@
         <v>0</v>
       </c>
       <c r="G152" t="str">
-        <v>[[10048,1,0],[10037,1,2.07],[10043,1,3.92],[10042,1,5.55],[10041,1,7.67],[10038,1,9.85],[10040,1,12.18],[10039,1,14.45],[10034,1,16.23],[20039,1,18.2],[20048,1,20.19],[20028,1,22.45],[20029,1,24.57],[20034,1,26.44],[30029,1,28.27],[30028,1,30.39],[30025,1,32.52],[30021,1,34.36],[30020,1,36.2],[40025,1,38.1],[40030,1,39.86],[40020,1,41.81],[40017,1,43.58]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H152">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I152">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J152">
         <v>1</v>
@@ -4831,13 +4824,13 @@
         <v>0</v>
       </c>
       <c r="G153" t="str">
-        <v>[[10048,1,0],[10037,1,1.88],[10043,1,4.15],[10042,1,6.29],[10041,1,8.01],[10038,1,10.26],[10040,1,12.28],[10039,1,14.02],[10034,1,16.1],[10045,1,18.18],[20039,1,20.32],[20048,1,22.33],[20028,1,24.51],[20029,1,26.68],[20034,1,29.01],[30029,1,31.12],[30028,1,33.29],[30025,1,35.2],[30021,1,37.47],[30020,1,39.18],[40025,1,41.14],[40030,1,43.38],[40020,1,45.52],[40017,1,47.88]]</v>
+        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
       </c>
       <c r="H153">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="I153">
-        <v>1.14</v>
+        <v>2.28</v>
       </c>
       <c r="J153">
         <v>1</v>
@@ -4860,13 +4853,13 @@
         <v>1</v>
       </c>
       <c r="G154" t="str">
-        <v>[[90039,1,0],[90040,1,2.99],[10048,1,5.88],[10037,1,7.96],[10043,1,10.02],[10042,1,11.65],[10038,1,13.37],[10041,1,15.14],[10040,1,16.95],[10039,1,19.35],[10045,1,21.18],[10034,1,22.82],[10046,1,24.53],[10047,1,26.83],[10044,1,29.19],[10033,1,31.37],[10030,1,33.42],[20039,1,35.13],[20048,1,37.14],[20028,1,39.31],[20034,1,41.14],[20029,1,42.87],[20040,1,44.54],[20038,1,46.67],[30029,1,48.39],[30028,1,50.43],[30025,1,52.36],[30021,1,54.74],[30020,1,56.63],[30030,1,58.64],[30027,1,60.92],[30018,1,62.56],[40025,1,64.61],[40030,1,66.97],[40020,1,68.63],[40017,1,70.48],[40027,1,72.1],[40031,1,74.2]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[10045,1],[10027,1],[20027,1],[20047,1],[30023,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H154">
-        <v>1.75</v>
+        <v>3.51</v>
       </c>
       <c r="I154">
-        <v>2.01</v>
+        <v>4.01</v>
       </c>
       <c r="J154">
         <v>1</v>
@@ -4889,13 +4882,13 @@
         <v>0</v>
       </c>
       <c r="G155" t="str">
-        <v>[[10048,1,0],[10037,1,2.01],[10043,1,3.72],[10041,1,5.42],[10042,1,7.38],[10038,1,9.71],[10040,1,11.55],[10039,1,13.61],[20039,1,15.76],[20048,1,18.07],[20040,1,19.71],[20038,1,21.96],[30029,1,24.23],[30028,1,26.5],[30025,1,28.42],[30030,1,30.44],[40025,1,32.29],[40030,1,34.19],[40027,1,35.86]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H155">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I155">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J155">
         <v>1</v>
@@ -4918,13 +4911,13 @@
         <v>0</v>
       </c>
       <c r="G156" t="str">
-        <v>[[10048,1,0],[10037,1,1.87],[10043,1,3.88],[10041,1,6.03],[10042,1,7.67],[10038,1,9.6],[10040,1,11.62],[10039,1,13.7],[10045,1,15.92],[10034,1,18.27],[20039,1,20.06],[20048,1,21.85],[20040,1,23.74],[20038,1,25.79],[20028,1,28.11],[30029,1,29.99],[30028,1,31.63],[30025,1,33.49],[30030,1,35.53],[30021,1,37.39],[40025,1,39.12],[40030,1,40.93],[40027,1,42.63],[40020,1,44.31]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H156">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I156">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J156">
         <v>1</v>
@@ -4947,13 +4940,13 @@
         <v>0</v>
       </c>
       <c r="G157" t="str">
-        <v>[[10048,1,0],[10037,1,2.18],[10043,1,4.2],[10041,1,5.83],[10042,1,8.14],[10038,1,10.31],[10040,1,11.98],[10039,1,13.87],[10045,1,15.67],[10034,1,17.61],[20039,1,19.61],[20048,1,21.7],[20040,1,23.76],[20038,1,26.1],[20028,1,27.87],[30029,1,30.12],[30028,1,32.51],[30025,1,34.59],[30030,1,36.27],[30021,1,38.46],[40025,1,40.52],[40030,1,42.14],[40027,1,43.75],[40020,1,45.64]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H157">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I157">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J157">
         <v>1</v>
@@ -4976,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="G158" t="str">
-        <v>[[10048,1,0],[10037,1,1.93],[10043,1,4.01],[10041,1,6.18],[10042,1,8.01],[10038,1,9.73],[10040,1,11.71],[10039,1,13.79],[10045,1,15.83],[10034,1,17.95],[20039,1,20.09],[20048,1,22.17],[20040,1,24.28],[20038,1,26.18],[20028,1,27.91],[30029,1,30.08],[30028,1,32.25],[30025,1,34.55],[30030,1,36.38],[30021,1,38.17],[40025,1,40.31],[40030,1,42.22],[40027,1,43.92],[40020,1,45.99]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H158">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I158">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J158">
         <v>1</v>
@@ -5005,13 +4998,13 @@
         <v>0</v>
       </c>
       <c r="G159" t="str">
-        <v>[[10048,1,0],[10037,1,1.7],[10043,1,4.07],[10041,1,5.75],[10042,1,7.53],[10038,1,9.26],[10040,1,11.51],[10039,1,13.58],[10045,1,15.72],[10034,1,17.51],[20039,1,19.14],[20048,1,21.46],[20040,1,23.57],[20038,1,25.52],[20028,1,27.81],[30029,1,29.51],[30028,1,31.74],[30025,1,33.66],[30030,1,35.31],[30021,1,37.6],[40025,1,39.22],[40030,1,41.59],[40027,1,43.87],[40020,1,45.68]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H159">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I159">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J159">
         <v>1</v>
@@ -5034,13 +5027,13 @@
         <v>0</v>
       </c>
       <c r="G160" t="str">
-        <v>[[10048,1,0],[10037,1,2.01],[10043,1,3.65],[10041,1,5.81],[10042,1,8.07],[10038,1,9.79],[10040,1,11.8],[10039,1,13.59],[10045,1,15.86],[10034,1,17.69],[20039,1,20.08],[20048,1,21.72],[20040,1,23.46],[20038,1,25.62],[20028,1,27.5],[30029,1,29.5],[30028,1,31.15],[30025,1,33.5],[30030,1,35.31],[30021,1,37.06],[40025,1,38.85],[40030,1,40.55],[40027,1,42.66],[40020,1,45.04]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H160">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I160">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J160">
         <v>1</v>
@@ -5063,13 +5056,13 @@
         <v>0</v>
       </c>
       <c r="G161" t="str">
-        <v>[[10048,1,0],[10037,1,1.65],[10043,1,3.35],[10041,1,5.69],[10042,1,7.95],[10038,1,9.8],[10040,1,12],[10039,1,13.78],[10045,1,15.42],[10034,1,17.65],[20039,1,19.51],[20048,1,21.31],[20040,1,23.09],[20038,1,24.95],[20028,1,27.1],[30029,1,29.04],[30028,1,31.21],[30025,1,33.39],[30030,1,35.26],[30021,1,36.95],[40025,1,38.71],[40030,1,40.63],[40027,1,42.51],[40020,1,44.35]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H161">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I161">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J161">
         <v>1</v>
@@ -5092,13 +5085,13 @@
         <v>0</v>
       </c>
       <c r="G162" t="str">
-        <v>[[10048,1,0],[10037,1,1.86],[10043,1,3.82],[10041,1,5.81],[10042,1,8.17],[10038,1,10.29],[10040,1,11.97],[10039,1,14.32],[10045,1,16.63],[10034,1,18.35],[20039,1,20.61],[20048,1,22.27],[20040,1,24.55],[20038,1,26.93],[20028,1,28.78],[30029,1,31.17],[30028,1,33.46],[30025,1,35.16],[30030,1,37.4],[30021,1,39.21],[40025,1,40.83],[40030,1,42.7],[40027,1,45.02],[40020,1,46.85]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H162">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I162">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -5121,13 +5114,13 @@
         <v>0</v>
       </c>
       <c r="G163" t="str">
-        <v>[[10048,1,0],[10037,1,2.18],[10043,1,4.27],[10041,1,6.28],[10042,1,8.04],[10038,1,10.17],[10040,1,12.07],[10039,1,13.69],[10045,1,15.53],[10034,1,17.45],[10046,1,19.32],[20039,1,21.4],[20048,1,23.34],[20040,1,25.2],[20038,1,27.08],[20028,1,28.7],[20034,1,30.79],[30029,1,33.08],[30028,1,34.7],[30025,1,36.51],[30030,1,38.35],[30021,1,40.65],[30020,1,42.64],[40025,1,44.64],[40030,1,46.34],[40027,1,48.74],[40020,1,50.79],[40017,1,52.89]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H163">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="I163">
-        <v>1.25</v>
+        <v>2.51</v>
       </c>
       <c r="J163">
         <v>1</v>
@@ -5150,13 +5143,13 @@
         <v>1</v>
       </c>
       <c r="G164" t="str">
-        <v>[[90039,1,0],[90040,1,2.34],[10048,1,5.08],[10037,1,7.28],[10043,1,9.67],[10042,1,11.41],[10038,1,13.43],[10041,1,15.51],[10040,1,17.42],[10039,1,19.25],[10045,1,21.19],[10046,1,23.55],[10034,1,25.62],[10047,1,27.59],[10044,1,29.75],[10033,1,32.08],[20039,1,33.97],[20048,1,35.68],[20040,1,37.37],[20038,1,39.75],[20028,1,41.54],[20034,1,43.22],[20046,1,45.62],[30029,1,47.31],[30028,1,49.54],[30025,1,51.49],[30030,1,53.77],[30021,1,55.54],[30020,1,57.7],[30027,1,59.64],[40025,1,61.39],[40030,1,63.75],[40027,1,66.06],[40020,1,67.79],[40017,1,69.72],[40023,1,71.53]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[10027,1],[10031,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H164">
-        <v>1.65</v>
+        <v>3.31</v>
       </c>
       <c r="I164">
-        <v>1.79</v>
+        <v>3.58</v>
       </c>
       <c r="J164">
         <v>1</v>
@@ -5179,13 +5172,13 @@
         <v>0</v>
       </c>
       <c r="G165" t="str">
-        <v>[[10048,1,0],[10037,1,2.33],[10043,1,3.93],[10041,1,6.33],[10042,1,8.17],[10038,1,10.34],[10040,1,12],[10039,1,13.63],[10045,1,15.69],[20039,1,17.4],[20048,1,19.74],[20040,1,21.48],[20038,1,23.52],[20028,1,25.43],[30029,1,27.52],[30028,1,29.53],[30025,1,31.19],[30030,1,32.95],[30021,1,35.15],[40025,1,36.8],[40030,1,39.03],[40027,1,41.15],[40020,1,42.86]]</v>
+        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H165">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I165">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J165">
         <v>1</v>
@@ -5208,13 +5201,13 @@
         <v>0</v>
       </c>
       <c r="G166" t="str">
-        <v>[[10048,1,0],[10037,1,2.2],[10043,1,4.27],[10041,1,5.87],[10042,1,7.57],[10038,1,9.88],[10040,1,12.15],[10039,1,14.21],[10045,1,16.39],[10046,1,18.39],[10034,1,20.47],[20039,1,22.84],[20048,1,24.61],[20040,1,26.33],[20038,1,28.44],[20028,1,30.8],[20034,1,32.68],[30029,1,34.68],[30028,1,37.04],[30025,1,38.75],[30030,1,40.7],[30021,1,42.89],[30020,1,44.74],[40025,1,47.14],[40030,1,49.27],[40027,1,51.41],[40020,1,53.53],[40017,1,55.35]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H166">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I166">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -5237,13 +5230,13 @@
         <v>0</v>
       </c>
       <c r="G167" t="str">
-        <v>[[10048,1,0],[10037,1,2.14],[10043,1,4.5],[10041,1,6.17],[10042,1,7.85],[10038,1,10.06],[10040,1,12.1],[10039,1,13.81],[10045,1,15.68],[10046,1,17.93],[10034,1,19.87],[20039,1,21.98],[20048,1,23.97],[20040,1,25.98],[20038,1,28.3],[20028,1,30.5],[20034,1,32.51],[30029,1,34.37],[30028,1,36],[30025,1,37.7],[30030,1,40.05],[30021,1,41.81],[30020,1,44.06],[40025,1,46.15],[40030,1,47.82],[40027,1,49.52],[40020,1,51.52],[40017,1,53.67]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H167">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I167">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J167">
         <v>1</v>
@@ -5266,13 +5259,13 @@
         <v>0</v>
       </c>
       <c r="G168" t="str">
-        <v>[[10048,1,0],[10037,1,1.66],[10043,1,3.86],[10041,1,5.53],[10042,1,7.85],[10038,1,9.79],[10040,1,11.91],[10039,1,13.86],[10045,1,15.85],[10046,1,17.57],[10034,1,19.82],[20039,1,21.74],[20048,1,23.96],[20040,1,26.03],[20038,1,27.97],[20028,1,30.12],[20034,1,31.97],[30029,1,33.93],[30028,1,35.79],[30025,1,37.99],[30030,1,39.75],[30021,1,41.52],[30020,1,43.59],[40025,1,45.94],[40030,1,48.03],[40027,1,50.17],[40020,1,51.8],[40017,1,53.63]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H168">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I168">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J168">
         <v>1</v>
@@ -5295,13 +5288,13 @@
         <v>0</v>
       </c>
       <c r="G169" t="str">
-        <v>[[10048,1,0],[10037,1,2.27],[10043,1,4.51],[10041,1,6.61],[10042,1,8.81],[10038,1,10.92],[10040,1,12.62],[10039,1,14.23],[10045,1,16.32],[10046,1,18.01],[10034,1,19.87],[20039,1,21.6],[20048,1,23.67],[20040,1,25.5],[20038,1,27.44],[20028,1,29.37],[20034,1,31.4],[30029,1,33],[30028,1,35.3],[30025,1,37.58],[30030,1,39.44],[30021,1,41.6],[30020,1,43.66],[40025,1,45.83],[40030,1,48.12],[40027,1,50.03],[40020,1,51.93],[40017,1,53.9]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H169">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I169">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J169">
         <v>1</v>
@@ -5324,13 +5317,13 @@
         <v>0</v>
       </c>
       <c r="G170" t="str">
-        <v>[[10048,1,0],[10037,1,2.12],[10043,1,3.87],[10041,1,5.63],[10042,1,7.39],[10038,1,9.17],[10040,1,11.51],[10039,1,13.86],[10045,1,16.22],[10046,1,17.95],[10034,1,20.3],[20039,1,22.36],[20048,1,24.25],[20040,1,26.37],[20038,1,28.53],[20028,1,30.73],[20034,1,32.82],[30029,1,34.9],[30028,1,36.64],[30025,1,38.58],[30030,1,40.65],[30021,1,42.86],[30020,1,44.51],[40025,1,46.56],[40030,1,48.88],[40027,1,51.13],[40020,1,53.37],[40017,1,55.52]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H170">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I170">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J170">
         <v>1</v>
@@ -5353,13 +5346,13 @@
         <v>0</v>
       </c>
       <c r="G171" t="str">
-        <v>[[10048,1,0],[10037,1,1.91],[10043,1,4.22],[10041,1,6.28],[10042,1,8.34],[10038,1,10.37],[10040,1,12.3],[10039,1,13.94],[10045,1,16.02],[10046,1,17.97],[10034,1,20.22],[20039,1,22.41],[20048,1,24.58],[20040,1,26.41],[20038,1,28.73],[20028,1,30.38],[20034,1,32.72],[30029,1,35.11],[30028,1,36.79],[30025,1,38.76],[30030,1,40.65],[30021,1,42.99],[30020,1,45.3],[40025,1,46.93],[40030,1,48.81],[40027,1,51.19],[40020,1,53.36],[40017,1,55.39]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H171">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I171">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J171">
         <v>1</v>
@@ -5382,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="G172" t="str">
-        <v>[[10048,1,0],[10037,1,2.12],[10043,1,4.31],[10041,1,6.5],[10042,1,8.6],[10038,1,10.32],[10040,1,12.64],[10039,1,14.5],[10045,1,16.61],[10046,1,18.83],[10034,1,20.92],[20039,1,22.84],[20048,1,24.59],[20040,1,26.26],[20038,1,28.52],[20028,1,30.49],[20034,1,32.73],[30029,1,34.99],[30028,1,36.67],[30025,1,38.81],[30030,1,41.11],[30021,1,43.19],[30020,1,45.03],[40025,1,46.77],[40030,1,48.85],[40027,1,50.65],[40020,1,52.75],[40017,1,54.53]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H172">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I172">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J172">
         <v>1</v>
@@ -5411,13 +5404,13 @@
         <v>0</v>
       </c>
       <c r="G173" t="str">
-        <v>[[10048,1,0],[10037,1,1.65],[10043,1,3.6],[10041,1,5.66],[10042,1,7.92],[10038,1,9.7],[10040,1,12.02],[10039,1,14.39],[10045,1,16.24],[10046,1,18.57],[10034,1,20.8],[10047,1,22.67],[20039,1,24.58],[20048,1,26.28],[20040,1,28.08],[20038,1,30.36],[20028,1,32.46],[20034,1,34.27],[30029,1,36.61],[30028,1,38.72],[30025,1,41.01],[30030,1,43.07],[30021,1,45.03],[30020,1,46.93],[30018,1,48.8],[40025,1,50.74],[40030,1,52.5],[40027,1,54.69],[40020,1,56.74],[40017,1,58.45]]</v>
+        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H173">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="I173">
-        <v>1.38</v>
+        <v>2.76</v>
       </c>
       <c r="J173">
         <v>1</v>
@@ -5440,13 +5433,13 @@
         <v>1</v>
       </c>
       <c r="G174" t="str">
-        <v>[[90039,1,0],[90040,1,2.82],[10048,1,5.77],[10037,1,7.44],[10043,1,9.51],[10042,1,11.62],[10038,1,13.46],[10041,1,15.34],[10040,1,17.59],[10039,1,19.48],[10045,1,21.24],[10046,1,23.13],[10047,1,25.04],[10034,1,26.83],[10044,1,29.08],[10033,1,31.1],[10030,1,32.84],[10035,1,35.19],[20039,1,37.32],[20048,1,39.26],[20038,1,41.16],[20040,1,43.17],[20028,1,45.03],[20034,1,47.21],[20046,1,48.88],[20041,1,50.9],[30029,1,53.19],[30028,1,55.57],[30025,1,57.75],[30030,1,59.61],[30021,1,61.42],[30020,1,63.52],[30018,1,65.67],[30027,1,67.71],[30019,1,70],[40025,1,71.95],[40030,1,73.58],[40027,1,75.86],[40020,1,77.69],[40017,1,79.43],[40031,1,81.81],[40023,1,83.45]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[10027,1],[10045,1],[20047,1],[20027,1],[30030,1],[30023,1],[40019,1],[40017,1]]</v>
       </c>
       <c r="H174">
-        <v>1.82</v>
+        <v>3.64</v>
       </c>
       <c r="I174">
-        <v>1.97</v>
+        <v>3.94</v>
       </c>
       <c r="J174">
         <v>1</v>
@@ -5469,13 +5462,13 @@
         <v>0</v>
       </c>
       <c r="G175" t="str">
-        <v>[[10048,1,0],[10037,1,1.98],[10043,1,4.38],[10042,1,6.28],[10041,1,7.96],[10038,1,10.09],[10040,1,11.72],[10039,1,13.87],[10045,1,16.2],[10046,1,17.85],[20039,1,19.73],[20048,1,22.06],[20040,1,23.89],[20038,1,25.6],[20046,1,27.22],[30029,1,29.42],[30025,1,31.8],[30028,1,34.05],[30030,1,36.24],[30027,1,37.97],[40025,1,39.69],[40030,1,41.53],[40027,1,43.29],[40031,1,45.16]]</v>
+        <v>[[10037,1],[10045,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H175">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I175">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J175">
         <v>1</v>
@@ -5498,13 +5491,13 @@
         <v>0</v>
       </c>
       <c r="G176" t="str">
-        <v>[[10048,1,0],[10037,1,1.87],[10043,1,3.97],[10042,1,5.82],[10041,1,7.9],[10038,1,9.81],[10040,1,12.1],[10039,1,14.23],[10045,1,16.24],[10046,1,18.47],[10047,1,20.79],[10044,1,22.51],[20039,1,24.74],[20048,1,27.01],[20040,1,28.63],[20038,1,30.52],[20046,1,32.39],[20041,1,34.53],[30029,1,36.74],[30025,1,39.01],[30028,1,40.67],[30030,1,42.71],[30027,1,44.8],[30031,1,47.1],[40025,1,49.27],[40030,1,51.27],[40027,1,53.62],[40031,1,56],[40020,1,58.01]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H176">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I176">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J176">
         <v>1</v>
@@ -5527,13 +5520,13 @@
         <v>0</v>
       </c>
       <c r="G177" t="str">
-        <v>[[10048,1,0],[10037,1,1.83],[10043,1,3.6],[10042,1,5.76],[10041,1,8.08],[10038,1,10.2],[10040,1,12.54],[10039,1,14.38],[10045,1,16.45],[10046,1,18.25],[10047,1,20.44],[10044,1,22.37],[20039,1,24.62],[20048,1,26.24],[20040,1,28.26],[20038,1,30],[20046,1,31.87],[20041,1,34.22],[30029,1,36.06],[30025,1,38.37],[30028,1,40.24],[30030,1,42.46],[30027,1,44.76],[30031,1,46.5],[40025,1,48.42],[40030,1,50.82],[40027,1,52.53],[40031,1,54.84],[40020,1,57.12]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H177">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I177">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J177">
         <v>1</v>
@@ -5556,13 +5549,13 @@
         <v>0</v>
       </c>
       <c r="G178" t="str">
-        <v>[[10048,1,0],[10037,1,2.18],[10043,1,3.83],[10042,1,5.67],[10041,1,7.87],[10038,1,9.51],[10040,1,11.28],[10039,1,13.27],[10045,1,15.21],[10046,1,16.92],[10047,1,18.61],[10044,1,20.87],[20039,1,23.22],[20048,1,25.51],[20040,1,27.24],[20038,1,28.99],[20046,1,30.77],[20041,1,33.04],[30029,1,35.33],[30025,1,37.68],[30028,1,39.84],[30030,1,41.84],[30027,1,44.05],[30031,1,46.13],[40025,1,47.88],[40030,1,50.13],[40027,1,51.82],[40031,1,53.75],[40020,1,56.04]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H178">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I178">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J178">
         <v>1</v>
@@ -5585,13 +5578,13 @@
         <v>0</v>
       </c>
       <c r="G179" t="str">
-        <v>[[10048,1,0],[10037,1,2.16],[10043,1,4.07],[10042,1,6.38],[10041,1,7.98],[10038,1,9.78],[10040,1,11.57],[10039,1,13.5],[10045,1,15.83],[10046,1,18.23],[10047,1,20.42],[10044,1,22.37],[20039,1,24.37],[20048,1,26.26],[20040,1,28.52],[20038,1,30.63],[20046,1,32.81],[20041,1,34.49],[30029,1,36.1],[30025,1,38.13],[30028,1,40.27],[30030,1,42.54],[30027,1,44.94],[30031,1,46.89],[40025,1,49.03],[40030,1,51.41],[40027,1,53.13],[40031,1,55.16],[40020,1,57.43]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H179">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I179">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J179">
         <v>1</v>
@@ -5614,13 +5607,13 @@
         <v>0</v>
       </c>
       <c r="G180" t="str">
-        <v>[[10048,1,0],[10037,1,1.95],[10043,1,3.64],[10042,1,5.97],[10041,1,7.67],[10038,1,9.88],[10040,1,11.49],[10039,1,13.32],[10045,1,15.19],[10046,1,17.54],[10047,1,19.24],[10044,1,20.84],[20039,1,22.85],[20048,1,24.88],[20040,1,26.63],[20038,1,28.94],[20046,1,31.31],[20041,1,32.93],[30029,1,34.66],[30025,1,36.4],[30028,1,38.72],[30030,1,40.69],[30027,1,42.83],[30031,1,44.59],[40025,1,46.98],[40030,1,49.2],[40027,1,51.5],[40031,1,53.1],[40020,1,55.12]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H180">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I180">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J180">
         <v>1</v>
@@ -5643,13 +5636,13 @@
         <v>0</v>
       </c>
       <c r="G181" t="str">
-        <v>[[10048,1,0],[10037,1,1.62],[10043,1,3.27],[10042,1,4.94],[10041,1,7.13],[10038,1,9.33],[10040,1,10.94],[10039,1,13.06],[10045,1,15.13],[10046,1,16.85],[10047,1,18.56],[10044,1,20.76],[20039,1,22.36],[20048,1,24.38],[20040,1,26.68],[20038,1,28.58],[20046,1,30.26],[20041,1,32.24],[30029,1,34.43],[30025,1,36.52],[30028,1,38.39],[30030,1,40.07],[30027,1,41.92],[30031,1,44],[40025,1,45.67],[40030,1,47.99],[40027,1,50.12],[40031,1,52.07],[40020,1,53.95]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H181">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I181">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J181">
         <v>1</v>
@@ -5672,13 +5665,13 @@
         <v>0</v>
       </c>
       <c r="G182" t="str">
-        <v>[[10048,1,0],[10037,1,2.23],[10043,1,4.23],[10042,1,5.94],[10041,1,8.08],[10038,1,9.89],[10040,1,11.49],[10039,1,13.41],[10045,1,15.76],[10046,1,17.89],[10047,1,19.75],[10044,1,21.38],[20039,1,23.74],[20048,1,25.52],[20040,1,27.87],[20038,1,30.24],[20046,1,32.62],[20041,1,34.81],[30029,1,36.43],[30025,1,38.2],[30028,1,40.01],[30030,1,42.22],[30027,1,44.03],[30031,1,46.28],[40025,1,48.33],[40030,1,50.49],[40027,1,52.15],[40031,1,53.88],[40020,1,56.01]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H182">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I182">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J182">
         <v>1</v>
@@ -5701,13 +5694,13 @@
         <v>0</v>
       </c>
       <c r="G183" t="str">
-        <v>[[10048,1,0],[10037,1,2.05],[10043,1,3.79],[10042,1,5.61],[10041,1,7.24],[10038,1,9.31],[10040,1,11.24],[10039,1,13.02],[10045,1,15.11],[10046,1,17.18],[10047,1,19.31],[10044,1,21.55],[10033,1,23.69],[10034,1,25.33],[20039,1,27.09],[20048,1,29.12],[20040,1,30.95],[20038,1,32.57],[20046,1,34.51],[20041,1,36.19],[20028,1,38.18],[30029,1,40],[30025,1,41.66],[30028,1,43.55],[30030,1,45.42],[30027,1,47.6],[30031,1,49.3],[30021,1,51.53],[40025,1,53.21],[40030,1,55.42],[40027,1,57.18],[40031,1,58.97],[40020,1,61.2],[40017,1,63.5]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H183">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="I183">
-        <v>1.52</v>
+        <v>3.03</v>
       </c>
       <c r="J183">
         <v>1</v>
@@ -5730,13 +5723,13 @@
         <v>1</v>
       </c>
       <c r="G184" t="str">
-        <v>[[90039,1,0],[90040,1,2.22],[10048,1,4.44],[10037,1,6.25],[10043,1,8.51],[10042,1,10.86],[10041,1,13.2],[10038,1,15.09],[10040,1,16.83],[10039,1,18.9],[10045,1,21.05],[10046,1,22.76],[10047,1,25.14],[10044,1,27.15],[10033,1,29],[10034,1,30.91],[10030,1,33.09],[10035,1,35.13],[10028,1,37.42],[10032,1,39.77],[10027,1,41.66],[20039,1,43.88],[20048,1,45.8],[20038,1,47.63],[20040,1,49.59],[20046,1,51.36],[20041,1,53.23],[20028,1,55.33],[20044,1,56.97],[30029,1,59.19],[30028,1,60.84],[30025,1,62.8],[30030,1,64.64],[30027,1,66.38],[30031,1,68.32],[30021,1,70.34],[30032,1,72.57],[30020,1,74.78],[40025,1,76.4],[40030,1,78.44],[40027,1,80.36],[40031,1,82.02],[40020,1,83.91],[40017,1,85.52],[40028,1,87.87]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10045,1],[10032,1],[10048,1],[20047,1],[20027,1],[30030,1],[30023,1],[40019,1],[40017,1]]</v>
       </c>
       <c r="H184">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I184">
-        <v>2.17</v>
+        <v>4.34</v>
       </c>
       <c r="J184">
         <v>1</v>
@@ -5759,13 +5752,13 @@
         <v>0</v>
       </c>
       <c r="G185" t="str">
-        <v>[[10048,1,0],[10037,1,2.09],[10043,1,4.49],[10042,1,6.58],[10041,1,8.85],[10040,1,10.56],[10038,1,12.72],[10039,1,14.68],[10045,1,17.05],[10046,1,19.14],[10047,1,21.3],[10033,1,23.39],[20039,1,25.53],[20048,1,27.41],[20038,1,29.6],[20040,1,31.8],[20046,1,34],[20041,1,35.74],[30029,1,37.83],[30028,1,39.76],[30025,1,42],[30030,1,44.11],[30027,1,45.91],[30021,1,48.29],[40025,1,50.67],[40030,1,52.38],[40027,1,54.05],[40031,1,56]]</v>
+        <v>[[10037,1],[10045,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H185">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I185">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J185">
         <v>1</v>
@@ -5788,13 +5781,13 @@
         <v>0</v>
       </c>
       <c r="G186" t="str">
-        <v>[[10048,1,0],[10037,1,1.77],[10043,1,3.45],[10042,1,5.44],[10041,1,7.81],[10040,1,9.63],[10038,1,11.78],[10039,1,14.11],[10045,1,16.27],[10046,1,18.22],[10047,1,20.06],[10033,1,21.87],[10044,1,23.97],[10034,1,25.89],[20039,1,28.02],[20048,1,29.89],[20038,1,31.93],[20040,1,34.23],[20046,1,36.41],[20041,1,38.21],[20044,1,39.98],[30029,1,41.76],[30028,1,44.1],[30025,1,46.26],[30030,1,48.49],[30027,1,50.58],[30021,1,52.44],[30031,1,54.46],[40025,1,56.26],[40030,1,58.18],[40027,1,60.39],[40031,1,62.37],[40026,1,64.31]]</v>
+        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H186">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I186">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J186">
         <v>1</v>
@@ -5817,13 +5810,13 @@
         <v>0</v>
       </c>
       <c r="G187" t="str">
-        <v>[[10048,1,0],[10037,1,1.7],[10043,1,3.54],[10042,1,5.83],[10041,1,8.21],[10040,1,10.53],[10038,1,12.45],[10039,1,14.58],[10045,1,16.42],[10046,1,18.78],[10047,1,20.39],[10044,1,22.03],[10033,1,24.41],[10034,1,26.26],[20039,1,27.87],[20048,1,29.84],[20038,1,31.68],[20040,1,34.01],[20046,1,36.27],[20041,1,38.61],[20044,1,40.21],[30029,1,42.25],[30028,1,44.16],[30025,1,46.55],[30030,1,48.42],[30027,1,50.57],[30031,1,52.19],[30021,1,54.02],[40025,1,56.03],[40030,1,57.71],[40027,1,60.01],[40031,1,62.3],[40026,1,64.07]]</v>
+        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H187">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I187">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J187">
         <v>1</v>
@@ -5846,13 +5839,13 @@
         <v>0</v>
       </c>
       <c r="G188" t="str">
-        <v>[[10048,1,0],[10037,1,2.21],[10043,1,3.92],[10042,1,5.69],[10041,1,8.01],[10040,1,9.94],[10038,1,11.9],[10039,1,14.25],[10045,1,16.29],[10046,1,17.98],[10047,1,19.97],[10044,1,22.25],[10033,1,23.99],[10034,1,25.98],[20039,1,28.11],[20048,1,29.79],[20038,1,31.64],[20040,1,34.03],[20046,1,35.7],[20041,1,37.75],[20044,1,39.36],[30029,1,41.26],[30028,1,42.92],[30025,1,44.75],[30030,1,46.53],[30027,1,48.57],[30031,1,50.69],[30021,1,52.43],[40025,1,54.3],[40030,1,56.36],[40027,1,58.14],[40031,1,60.01],[40026,1,61.92]]</v>
+        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H188">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I188">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J188">
         <v>1</v>
@@ -5875,13 +5868,13 @@
         <v>0</v>
       </c>
       <c r="G189" t="str">
-        <v>[[10048,1,0],[10037,1,2.29],[10043,1,4.44],[10042,1,6.1],[10041,1,8.33],[10040,1,10.7],[10038,1,13.02],[10039,1,15.04],[10045,1,17.33],[10046,1,19.09],[10047,1,20.72],[10044,1,22.76],[10033,1,24.99],[10034,1,27.2],[20039,1,29.54],[20048,1,31.35],[20038,1,33.72],[20040,1,35.34],[20046,1,37.37],[20041,1,39.21],[20044,1,40.88],[30029,1,42.94],[30028,1,44.74],[30025,1,46.37],[30030,1,48.56],[30027,1,50.45],[30031,1,52.45],[30021,1,54.55],[40025,1,56.3],[40030,1,57.94],[40027,1,59.97],[40031,1,61.96],[40026,1,63.68]]</v>
+        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H189">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I189">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J189">
         <v>1</v>
@@ -5904,13 +5897,13 @@
         <v>0</v>
       </c>
       <c r="G190" t="str">
-        <v>[[10048,1,0],[10037,1,1.89],[10043,1,4.27],[10042,1,6.26],[10041,1,8.57],[10040,1,10.89],[10038,1,12.69],[10039,1,14.52],[10045,1,16.48],[10046,1,18.54],[10047,1,20.85],[10044,1,22.47],[10033,1,24.57],[10034,1,26.93],[20039,1,29.05],[20048,1,31.41],[20038,1,33.28],[20040,1,34.93],[20046,1,37.05],[20041,1,39.44],[20044,1,41.55],[30029,1,43.49],[30028,1,45.34],[30025,1,47.22],[30030,1,48.97],[30027,1,50.77],[30031,1,52.72],[30021,1,54.38],[40025,1,56.62],[40030,1,58.76],[40027,1,61.03],[40031,1,63.4],[40026,1,65.28]]</v>
+        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H190">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I190">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J190">
         <v>1</v>
@@ -5933,13 +5926,13 @@
         <v>0</v>
       </c>
       <c r="G191" t="str">
-        <v>[[10048,1,0],[10037,1,2.09],[10043,1,4.42],[10042,1,6.51],[10041,1,8.34],[10040,1,10.68],[10038,1,12.47],[10039,1,14.13],[10045,1,15.78],[10046,1,17.94],[10047,1,19.79],[10044,1,21.73],[10033,1,23.66],[10034,1,25.79],[20039,1,27.62],[20048,1,29.6],[20038,1,31.47],[20040,1,33.23],[20046,1,35.18],[20041,1,37.2],[20044,1,39.17],[30029,1,41.04],[30028,1,43.06],[30025,1,44.86],[30030,1,47.2],[30027,1,49.24],[30031,1,50.99],[30021,1,53.03],[40025,1,54.72],[40030,1,56.51],[40027,1,58.27],[40031,1,60.11],[40026,1,61.82]]</v>
+        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H191">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I191">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J191">
         <v>1</v>
@@ -5962,13 +5955,13 @@
         <v>0</v>
       </c>
       <c r="G192" t="str">
-        <v>[[10048,1,0],[10037,1,1.82],[10043,1,3.67],[10042,1,5.29],[10041,1,7.15],[10040,1,9.04],[10038,1,11.05],[10039,1,13.18],[10045,1,15.44],[10046,1,17.24],[10047,1,19.14],[10044,1,21.26],[10033,1,23.28],[10034,1,25.16],[20039,1,27.45],[20048,1,29.4],[20038,1,31.53],[20040,1,33.51],[20046,1,35.74],[20041,1,38.11],[20044,1,40.31],[30029,1,42.54],[30028,1,44.47],[30025,1,46.14],[30030,1,48.21],[30027,1,49.86],[30031,1,52.03],[30021,1,54.22],[40025,1,56.13],[40030,1,58.11],[40027,1,60.16],[40031,1,62.43],[40026,1,64.29]]</v>
+        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
       </c>
       <c r="H192">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I192">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J192">
         <v>1</v>
@@ -5991,13 +5984,13 @@
         <v>0</v>
       </c>
       <c r="G193" t="str">
-        <v>[[10048,1,0],[10037,1,2],[10043,1,3.65],[10042,1,5.72],[10041,1,7.87],[10040,1,10.12],[10038,1,12.42],[10039,1,14.34],[10045,1,16.33],[10046,1,18.12],[10047,1,19.94],[10044,1,22.29],[10033,1,24.57],[10034,1,26.41],[10030,1,28.7],[10035,1,30.45],[20039,1,32.49],[20048,1,34.14],[20038,1,36.27],[20040,1,38.56],[20046,1,40.33],[20041,1,42.69],[20044,1,44.37],[20028,1,46.53],[30029,1,48.89],[30028,1,50.69],[30025,1,52.91],[30030,1,55.27],[30027,1,57.22],[30031,1,59.14],[30021,1,61.3],[30032,1,63.28],[40025,1,65.58],[40030,1,67.31],[40027,1,69.33],[40031,1,71.14],[40026,1,73.32],[40020,1,75.61]]</v>
+        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[20027,1],[30030,1],[30023,1],[40019,2]]</v>
       </c>
       <c r="H193">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="I193">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="J193">
         <v>1</v>
@@ -6020,13 +6013,13 @@
         <v>1</v>
       </c>
       <c r="G194" t="str">
-        <v>[[90039,1,0],[90040,1,2.53],[10048,1,5.04],[10037,1,7.38],[10043,1,9.1],[10042,1,10.74],[10038,1,12.55],[10041,1,14.19],[10040,1,16.54],[10039,1,18.55],[10045,1,20.53],[10046,1,22.28],[10047,1,23.88],[10044,1,25.69],[10033,1,27.95],[10034,1,29.92],[10030,1,31.6],[10035,1,33.3],[10028,1,35.22],[10032,1,36.99],[10031,1,38.9],[10027,1,40.59],[10036,1,42.68],[10029,1,45.06],[20039,1,46.71],[20048,1,48.96],[20040,1,51.06],[20038,1,52.75],[20046,1,54.9],[20041,1,56.53],[20044,1,58.84],[20028,1,60.55],[20042,1,62.29],[30029,1,64.61],[30028,1,66.37],[30025,1,68.26],[30030,1,70.03],[30027,1,71.72],[30031,1,73.81],[30032,1,75.9],[30021,1,78.21],[30026,1,80.23],[30020,1,82.47],[40025,1,84.86],[40030,1,86.89],[40027,1,88.59],[40031,1,90.58],[40026,1,92.82],[40020,1,94.79],[40028,1,96.42],[40017,1,98.03]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10045,1],[10048,1],[10042,1],[20047,1],[20027,1],[30030,1],[30023,1],[40019,1],[40027,1]]</v>
       </c>
       <c r="H194">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="I194">
-        <v>2.39</v>
+        <v>4.77</v>
       </c>
       <c r="J194">
         <v>1</v>
@@ -6049,13 +6042,13 @@
         <v>0</v>
       </c>
       <c r="G195" t="str">
-        <v>[[10048,1,0],[10037,1,2.34],[10043,1,4.27],[10042,1,6.61],[10041,1,8.74],[10038,1,10.41],[10040,1,12.26],[10039,1,14.04],[10045,1,16.38],[10046,1,18.01],[10047,1,20.13],[10044,1,22.18],[10034,1,23.88],[20039,1,25.86],[20048,1,27.85],[20040,1,29.74],[20038,1,31.45],[20046,1,33.57],[20041,1,35.51],[20028,1,37.78],[30029,1,39.45],[30028,1,41.85],[30025,1,44.02],[30030,1,46.08],[30027,1,47.93],[30031,1,49.76],[30021,1,51.89],[40025,1,53.62],[40030,1,55.63],[40027,1,57.37],[40031,1,59.69],[40028,1,61.49]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40027,1]]</v>
       </c>
       <c r="H195">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I195">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J195">
         <v>1</v>
@@ -6078,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="G196" t="str">
-        <v>[[10048,1,0],[10037,1,1.76],[10043,1,3.45],[10042,1,5.22],[10041,1,7.45],[10038,1,9.31],[10040,1,11.22],[10039,1,12.87],[10045,1,14.64],[10046,1,16.35],[10047,1,18.49],[10044,1,20.26],[10034,1,22.09],[10033,1,23.69],[10030,1,25.54],[10035,1,27.89],[10028,1,29.53],[20039,1,31.38],[20048,1,33.3],[20040,1,35.24],[20038,1,37.4],[20046,1,39.53],[20041,1,41.27],[20028,1,42.88],[20044,1,44.81],[30029,1,47],[30028,1,49.09],[30025,1,51.26],[30030,1,52.96],[30027,1,54.83],[30031,1,57.08],[30021,1,59.16],[30032,1,61.15],[40025,1,62.95],[40030,1,64.63],[40027,1,66.95],[40031,1,69.34],[40028,1,71.28],[40020,1,73.26]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
       </c>
       <c r="H196">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I196">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J196">
         <v>1</v>
@@ -6107,13 +6100,13 @@
         <v>0</v>
       </c>
       <c r="G197" t="str">
-        <v>[[10048,1,0],[10037,1,2.28],[10043,1,4.42],[10042,1,6.39],[10041,1,8.74],[10038,1,11.01],[10040,1,12.78],[10039,1,14.81],[10045,1,16.56],[10046,1,18.42],[10047,1,20.21],[10044,1,22.09],[10034,1,23.7],[10033,1,25.59],[10030,1,27.76],[10035,1,29.39],[10028,1,31.42],[20039,1,33.23],[20048,1,35.51],[20040,1,37.59],[20038,1,39.52],[20046,1,41.77],[20041,1,44.17],[20044,1,46.36],[20028,1,48.28],[30029,1,50.27],[30028,1,52.14],[30025,1,54.03],[30030,1,56.18],[30027,1,58.38],[30031,1,60.35],[30032,1,62.21],[30021,1,64.18],[40025,1,66.46],[40030,1,68.72],[40027,1,71.04],[40031,1,72.65],[40028,1,75.05],[40020,1,77.38]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
       </c>
       <c r="H197">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I197">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J197">
         <v>1</v>
@@ -6136,13 +6129,13 @@
         <v>0</v>
       </c>
       <c r="G198" t="str">
-        <v>[[10048,1,0],[10037,1,1.82],[10043,1,3.76],[10042,1,5.82],[10041,1,7.46],[10038,1,9.79],[10040,1,11.42],[10039,1,13.5],[10045,1,15.28],[10046,1,17.24],[10047,1,18.97],[10044,1,21.36],[10034,1,23.63],[10033,1,25.87],[10030,1,27.61],[10035,1,29.68],[10028,1,31.34],[20039,1,33.05],[20048,1,35.13],[20040,1,37.36],[20038,1,39.04],[20046,1,40.8],[20041,1,42.43],[20044,1,44.41],[20028,1,46.62],[30029,1,48.83],[30028,1,50.99],[30025,1,52.91],[30030,1,54.84],[30027,1,56.55],[30031,1,58.22],[30032,1,60.17],[30021,1,62.07],[40025,1,63.7],[40030,1,65.38],[40027,1,67.11],[40031,1,69.42],[40028,1,71.03],[40020,1,72.77]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
       </c>
       <c r="H198">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I198">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J198">
         <v>1</v>
@@ -6165,13 +6158,13 @@
         <v>0</v>
       </c>
       <c r="G199" t="str">
-        <v>[[10048,1,0],[10037,1,2.14],[10043,1,4.23],[10042,1,6.09],[10041,1,8.44],[10038,1,10.19],[10040,1,11.95],[10039,1,14.01],[10045,1,16.03],[10046,1,18.03],[10047,1,20.39],[10044,1,22.05],[10034,1,24.07],[10033,1,25.74],[10030,1,27.94],[10035,1,29.88],[10028,1,32],[20039,1,33.9],[20048,1,35.57],[20040,1,37.91],[20038,1,39.76],[20046,1,41.58],[20041,1,43.49],[20044,1,45.54],[20028,1,47.77],[30029,1,49.8],[30028,1,51.54],[30025,1,53.7],[30030,1,55.51],[30027,1,57.17],[30031,1,59.16],[30032,1,61.21],[30021,1,62.92],[40025,1,65.07],[40030,1,67.23],[40027,1,69.42],[40031,1,71.51],[40028,1,73.56],[40020,1,75.28]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
       </c>
       <c r="H199">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I199">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J199">
         <v>1</v>
@@ -6194,13 +6187,13 @@
         <v>0</v>
       </c>
       <c r="G200" t="str">
-        <v>[[10048,1,0],[10037,1,2.19],[10043,1,4.21],[10042,1,6.46],[10041,1,8.31],[10038,1,10.58],[10040,1,12.41],[10039,1,14.74],[10045,1,16.55],[10046,1,18.85],[10047,1,20.97],[10044,1,23.07],[10034,1,25.06],[10033,1,26.81],[10030,1,28.47],[10035,1,30.68],[10028,1,32.44],[20039,1,34.38],[20048,1,36.3],[20040,1,38.13],[20038,1,39.79],[20046,1,41.52],[20041,1,43.79],[20044,1,45.93],[20028,1,47.83],[30029,1,49.61],[30028,1,51.66],[30025,1,53.64],[30030,1,55.36],[30027,1,57.69],[30031,1,59.43],[30032,1,61.18],[30021,1,62.81],[40025,1,64.78],[40030,1,67.13],[40027,1,68.91],[40031,1,71.15],[40028,1,72.83],[40020,1,74.49]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
       </c>
       <c r="H200">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I200">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J200">
         <v>1</v>
@@ -6223,13 +6216,13 @@
         <v>0</v>
       </c>
       <c r="G201" t="str">
-        <v>[[10048,1,0],[10037,1,2.26],[10043,1,4.15],[10042,1,6.13],[10041,1,8.46],[10038,1,10.26],[10040,1,12.43],[10039,1,14.05],[10045,1,16.42],[10046,1,18.17],[10047,1,20.06],[10044,1,22.23],[10034,1,24.22],[10033,1,25.85],[10030,1,28.17],[10035,1,30.48],[10028,1,32.57],[20039,1,34.62],[20048,1,36.5],[20040,1,38.84],[20038,1,40.64],[20046,1,42.73],[20041,1,44.42],[20044,1,46.82],[20028,1,49.13],[30029,1,51.25],[30028,1,52.96],[30025,1,54.73],[30030,1,56.48],[30027,1,58.58],[30031,1,60.77],[30032,1,63.13],[30021,1,65.16],[40025,1,67.12],[40030,1,69.43],[40027,1,71.82],[40031,1,73.91],[40028,1,75.85],[40020,1,77.75]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
       </c>
       <c r="H201">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I201">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J201">
         <v>1</v>
@@ -6252,13 +6245,13 @@
         <v>0</v>
       </c>
       <c r="G202" t="str">
-        <v>[[10048,1,0],[10037,1,1.73],[10043,1,3.74],[10042,1,5.65],[10041,1,7.38],[10038,1,9.12],[10040,1,10.96],[10039,1,13.2],[10045,1,15.27],[10046,1,17.63],[10047,1,19.73],[10044,1,21.48],[10034,1,23.43],[10033,1,25.13],[10030,1,26.8],[10035,1,29.04],[10028,1,31.31],[20039,1,33.51],[20048,1,35.32],[20040,1,37.34],[20038,1,39.23],[20046,1,41.22],[20041,1,42.97],[20044,1,45.36],[20028,1,47.22],[30029,1,48.88],[30028,1,50.56],[30025,1,52.79],[30030,1,55.06],[30027,1,56.97],[30031,1,58.69],[30032,1,60.72],[30021,1,62.68],[40025,1,64.57],[40030,1,66.63],[40027,1,68.56],[40031,1,70.64],[40028,1,72.45],[40020,1,74.08]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
       </c>
       <c r="H202">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I202">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J202">
         <v>1</v>
@@ -6281,13 +6274,13 @@
         <v>0</v>
       </c>
       <c r="G203" t="str">
-        <v>[[10048,1,0],[10037,1,2.39],[10043,1,4.52],[10042,1,6.57],[10041,1,8.75],[10038,1,10.89],[10040,1,12.62],[10039,1,14.4],[10045,1,16.1],[10046,1,17.78],[10047,1,19.7],[10044,1,21.66],[10034,1,23.65],[10033,1,25.49],[10030,1,27.73],[10035,1,29.47],[10028,1,31.6],[10032,1,33.41],[10027,1,35.25],[20039,1,37.3],[20048,1,39.1],[20040,1,41.35],[20038,1,43.22],[20046,1,45.19],[20041,1,47.38],[20044,1,49.48],[20028,1,51.3],[20042,1,53.09],[30029,1,54.94],[30028,1,57.1],[30025,1,59.2],[30030,1,61.35],[30027,1,63.33],[30031,1,64.94],[30032,1,66.73],[30021,1,68.73],[30020,1,70.43],[40025,1,72.12],[40030,1,74.5],[40027,1,76.26],[40031,1,78.38],[40028,1,80.35],[40020,1,82.55],[40026,1,84.88]]</v>
+        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
       </c>
       <c r="H203">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="I203">
-        <v>1.83</v>
+        <v>3.67</v>
       </c>
       <c r="J203">
         <v>1</v>
@@ -6310,13 +6303,13 @@
         <v>1</v>
       </c>
       <c r="G204" t="str">
-        <v>[[90039,1,0],[90040,1,2.43],[10048,1,5.17],[10037,1,7.02],[10043,1,8.95],[10042,1,10.76],[10038,1,12.38],[10041,1,14.38],[10040,1,16.31],[10039,1,18.32],[10045,1,20.71],[10046,1,22.56],[10047,1,24.23],[10044,1,26.49],[10034,1,28.28],[10033,1,30.38],[10030,1,31.99],[10035,1,34.32],[10028,1,36.58],[10032,1,38.28],[10027,1,40.05],[10031,1,42.19],[10036,1,44.39],[10029,1,46.68],[10025,1,48.73],[10026,1,50.51],[20039,1,52.62],[20048,1,54.51],[20040,1,56.23],[20038,1,58.02],[20046,1,60.37],[20041,1,62.17],[20044,1,64.38],[20042,1,66.51],[20028,1,68.12],[20043,1,70.41],[20047,1,72.44],[20045,1,74.78],[30029,1,76.98],[30028,1,78.66],[30030,1,80.69],[30025,1,82.36],[30027,1,84.23],[30031,1,86.15],[30032,1,88.02],[30021,1,89.8],[30020,1,92.17],[30026,1,94.08],[30018,1,96.33],[30019,1,98.25],[30024,1,100.39],[30023,1,102.69],[40025,1,104.51],[40030,1,106.89],[40027,1,109.19],[40031,1,111.3],[40028,1,112.98],[40026,1,115.08],[40020,1,117.36],[40029,1,119.1],[40032,1,121.26],[40023,1,123.55]]</v>
+        <v>[[90039,1],[90040,1],[10037,1],[10045,1],[10032,1],[10027,1],[10048,1],[10042,1],[20047,1],[20027,1],[20043,1],[30030,1],[30023,1],[30025,1],[40027,1],[40032,1]]</v>
       </c>
       <c r="H204">
-        <v>2.83</v>
+        <v>5.65</v>
       </c>
       <c r="I204">
-        <v>3.23</v>
+        <v>6.46</v>
       </c>
       <c r="J204">
         <v>1</v>

--- a/public/StageStepTable.xlsx
+++ b/public/StageStepTable.xlsx
@@ -532,7 +532,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H5">
         <v>0.6</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
       </c>
       <c r="H6">
         <v>0.6</v>
@@ -590,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H7">
         <v>0.6</v>
@@ -619,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H8">
         <v>0.6</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
       </c>
       <c r="H9">
         <v>0.6</v>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H10">
         <v>0.6</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H11">
         <v>0.6</v>
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
       </c>
       <c r="H12">
         <v>0.6</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H13">
         <v>0.6</v>
@@ -793,7 +793,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="str">
-        <v>[[90033,1],[90034,1],[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[90033,2],[90034,3],[10002,4],[20002,10],[30004,11],[40001,17]]</v>
       </c>
       <c r="H14">
         <v>0.79</v>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
       </c>
       <c r="H15">
         <v>0.66</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H16">
         <v>0.66</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H17">
         <v>0.66</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
       </c>
       <c r="H18">
         <v>0.66</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H19">
         <v>0.66</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H20">
         <v>0.66</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
       </c>
       <c r="H21">
         <v>0.66</v>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H22">
         <v>0.66</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H23">
         <v>0.66</v>
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v>[[90033,1],[90034,1],[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[90033,2],[90034,3],[10002,4],[10009,10],[20002,11],[30004,17],[40001,18]]</v>
       </c>
       <c r="H24">
         <v>0.87</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H25">
         <v>0.73</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H26">
         <v>0.73</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
       </c>
       <c r="H27">
         <v>0.73</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H28">
         <v>0.73</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H29">
         <v>0.73</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
       </c>
       <c r="H30">
         <v>0.73</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
       </c>
       <c r="H31">
         <v>0.73</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H32">
         <v>0.73</v>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
       </c>
       <c r="H33">
         <v>0.73</v>
@@ -1373,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="str">
-        <v>[[90035,1],[90036,1],[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[90035,2],[90036,3],[10002,4],[10009,10],[20002,11],[30004,17],[40001,18]]</v>
       </c>
       <c r="H34">
         <v>0.96</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="str">
-        <v>[[10002,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H35">
         <v>0.8</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
       </c>
       <c r="H36">
         <v>0.8</v>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
       </c>
       <c r="H37">
         <v>0.8</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H38">
         <v>0.8</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
       </c>
       <c r="H39">
         <v>0.8</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
       </c>
       <c r="H40">
         <v>0.8</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H41">
         <v>0.8</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
       </c>
       <c r="H42">
         <v>0.8</v>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
       </c>
       <c r="H43">
         <v>0.8</v>
@@ -1663,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="str">
-        <v>[[90035,1],[90036,1],[10002,1],[10009,1],[10012,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[90035,3],[90036,4],[10002,10],[10009,11],[10012,17],[20002,18],[30004,12],[40001,5]]</v>
       </c>
       <c r="H44">
         <v>1.05</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
       </c>
       <c r="H45">
         <v>0.88</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
       </c>
       <c r="H46">
         <v>0.88</v>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H47">
         <v>0.88</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
       </c>
       <c r="H48">
         <v>0.88</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
       </c>
       <c r="H49">
         <v>0.88</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H50">
         <v>0.88</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
       </c>
       <c r="H51">
         <v>0.88</v>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
       </c>
       <c r="H52">
         <v>0.88</v>
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="str">
-        <v>[[10002,1],[10009,1],[20002,1],[30004,1],[40001,1]]</v>
+        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
       </c>
       <c r="H53">
         <v>0.88</v>
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="str">
-        <v>[[90035,1],[90036,1],[10002,1],[10009,1],[10014,1],[20002,1],[20004,1],[30004,1],[30007,1],[40001,1]]</v>
+        <v>[[90035,3],[90036,4],[10002,10],[10009,11],[10014,17],[20002,18],[20004,12],[30004,5],[30007,19],[40001,2]]</v>
       </c>
       <c r="H54">
         <v>1.35</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
       </c>
       <c r="H55">
         <v>0.97</v>
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H56">
         <v>0.97</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
       </c>
       <c r="H57">
         <v>0.97</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
       </c>
       <c r="H58">
         <v>0.97</v>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H59">
         <v>0.97</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
       </c>
       <c r="H60">
         <v>0.97</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
       </c>
       <c r="H61">
         <v>0.97</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H62">
         <v>0.97</v>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
       </c>
       <c r="H63">
         <v>0.97</v>
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="G64" t="str">
-        <v>[[90037,1],[90038,1],[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[90037,2],[90038,3],[10014,4],[10022,10],[20014,11],[30014,17],[40014,18]]</v>
       </c>
       <c r="H64">
         <v>1.28</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H65">
         <v>1.06</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
       </c>
       <c r="H66">
         <v>1.06</v>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
       </c>
       <c r="H67">
         <v>1.06</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H68">
         <v>1.06</v>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
       </c>
       <c r="H69">
         <v>1.06</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
       </c>
       <c r="H70">
         <v>1.06</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H71">
         <v>1.06</v>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
       </c>
       <c r="H72">
         <v>1.06</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[10022,4],[20014,5],[30014,10],[40014,11]]</v>
       </c>
       <c r="H73">
         <v>1.06</v>
@@ -2533,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="str">
-        <v>[[90037,1],[90038,1],[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[90037,2],[90038,3],[10014,4],[10022,10],[20014,11],[30014,17],[40014,18]]</v>
       </c>
       <c r="H74">
         <v>1.4</v>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="str">
-        <v>[[10014,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
       </c>
       <c r="H75">
         <v>1.17</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[10022,4],[20014,5],[30014,10],[40014,11]]</v>
       </c>
       <c r="H76">
         <v>1.17</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[10022,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H77">
         <v>1.17</v>
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[10022,4],[20014,10],[30014,11],[40014,17]]</v>
       </c>
       <c r="H78">
         <v>1.17</v>
@@ -2678,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[10022,4],[20014,5],[30014,10],[40014,11]]</v>
       </c>
       <c r="H79">
         <v>1.17</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[10022,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H80">
         <v>1.17</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[10022,4],[20014,10],[30014,11],[40014,17]]</v>
       </c>
       <c r="H81">
         <v>1.17</v>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,3],[10022,4],[20014,5],[30014,10],[40014,11]]</v>
       </c>
       <c r="H82">
         <v>1.17</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="str">
-        <v>[[10014,1],[10022,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[10014,2],[10022,3],[20014,4],[30014,10],[40014,11]]</v>
       </c>
       <c r="H83">
         <v>1.17</v>
@@ -2823,7 +2823,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="str">
-        <v>[[90037,1],[90038,1],[10014,1],[10022,1],[10017,1],[20014,1],[30014,1],[40014,1]]</v>
+        <v>[[90037,3],[90038,4],[10014,10],[10022,11],[10017,17],[20014,18],[30014,12],[40014,5]]</v>
       </c>
       <c r="H84">
         <v>1.54</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H85">
         <v>1.29</v>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H86">
         <v>1.29</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H87">
         <v>1.29</v>
@@ -2939,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H88">
         <v>1.29</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H89">
         <v>1.29</v>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H90">
         <v>1.29</v>
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H91">
         <v>1.29</v>
@@ -3055,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H92">
         <v>1.29</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H93">
         <v>1.29</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="G94" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[90039,3],[90040,4],[10037,10],[20027,11],[30023,17],[40019,18]]</v>
       </c>
       <c r="H94">
         <v>1.7</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H95">
         <v>1.41</v>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H96">
         <v>1.41</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H97">
         <v>1.41</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H98">
         <v>1.41</v>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H99">
         <v>1.41</v>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H100">
         <v>1.41</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H101">
         <v>1.41</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H102">
         <v>1.41</v>
@@ -3374,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H103">
         <v>1.41</v>
@@ -3403,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="G104" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[90039,2],[90040,3],[10037,4],[10032,10],[20027,11],[30023,17],[40019,18]]</v>
       </c>
       <c r="H104">
         <v>2.18</v>
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H105">
         <v>1.56</v>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H106">
         <v>1.56</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H107">
         <v>1.56</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H108">
         <v>1.56</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H109">
         <v>1.56</v>
@@ -3577,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H110">
         <v>1.56</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H111">
         <v>1.56</v>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H112">
         <v>1.56</v>
@@ -3664,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H113">
         <v>1.56</v>
@@ -3693,7 +3693,7 @@
         <v>1</v>
       </c>
       <c r="G114" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[90039,2],[90040,3],[10037,4],[10032,10],[20027,11],[30023,17],[40019,18]]</v>
       </c>
       <c r="H114">
         <v>2.05</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H115">
         <v>1.71</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H116">
         <v>1.71</v>
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H117">
         <v>1.71</v>
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H118">
         <v>1.71</v>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H119">
         <v>1.71</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H120">
         <v>1.71</v>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H121">
         <v>1.71</v>
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H122">
         <v>1.71</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H123">
         <v>1.71</v>
@@ -3983,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="G124" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10045,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[90039,2],[90040,3],[10037,4],[10045,10],[20027,11],[30023,17],[40019,18]]</v>
       </c>
       <c r="H124">
         <v>2.26</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H125">
         <v>1.88</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H126">
         <v>1.88</v>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H127">
         <v>1.88</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H128">
         <v>1.88</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H129">
         <v>1.88</v>
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H130">
         <v>1.88</v>
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H131">
         <v>1.88</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H132">
         <v>1.88</v>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
       </c>
       <c r="H133">
         <v>1.88</v>
@@ -4273,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[90039,2],[90040,3],[10037,4],[10032,10],[20027,11],[30023,17],[40019,18]]</v>
       </c>
       <c r="H134">
         <v>2.49</v>
@@ -4302,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="str">
-        <v>[[10037,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
       </c>
       <c r="H135">
         <v>2.07</v>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
       </c>
       <c r="H136">
         <v>2.07</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H137">
         <v>2.07</v>
@@ -4389,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
       </c>
       <c r="H138">
         <v>2.07</v>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
       </c>
       <c r="H139">
         <v>2.07</v>
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H140">
         <v>2.07</v>
@@ -4476,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
       </c>
       <c r="H141">
         <v>2.07</v>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
       </c>
       <c r="H142">
         <v>2.07</v>
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H143">
         <v>2.07</v>
@@ -4563,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[10027,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[90039,3],[90040,4],[10037,10],[10032,11],[10027,17],[20027,18],[30023,12],[40019,5]]</v>
       </c>
       <c r="H144">
         <v>2.73</v>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
       </c>
       <c r="H145">
         <v>2.28</v>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H146">
         <v>2.28</v>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
       </c>
       <c r="H147">
         <v>2.28</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
       </c>
       <c r="H148">
         <v>2.28</v>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H149">
         <v>2.28</v>
@@ -4737,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
       </c>
       <c r="H150">
         <v>2.28</v>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
       </c>
       <c r="H151">
         <v>2.28</v>
@@ -4795,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
       </c>
       <c r="H152">
         <v>2.28</v>
@@ -4824,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="str">
-        <v>[[10037,1],[10032,1],[20027,1],[30023,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
       </c>
       <c r="H153">
         <v>2.28</v>
@@ -4853,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[10045,1],[10027,1],[20027,1],[20047,1],[30023,1],[30030,1],[40019,1]]</v>
+        <v>[[90039,3],[90040,4],[10037,10],[10032,11],[10045,17],[10027,18],[20027,12],[20047,5],[30023,19],[30030,2],[40019,9]]</v>
       </c>
       <c r="H154">
         <v>3.51</v>
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20047,4],[30030,10],[40019,11]]</v>
       </c>
       <c r="H155">
         <v>2.51</v>
@@ -4911,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H156">
         <v>2.51</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20047,5],[30030,10],[40019,11]]</v>
       </c>
       <c r="H157">
         <v>2.51</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20047,4],[30030,10],[40019,11]]</v>
       </c>
       <c r="H158">
         <v>2.51</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H159">
         <v>2.51</v>
@@ -5027,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20047,5],[30030,10],[40019,11]]</v>
       </c>
       <c r="H160">
         <v>2.51</v>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[20047,4],[30030,10],[40019,11]]</v>
       </c>
       <c r="H161">
         <v>2.51</v>
@@ -5085,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H162">
         <v>2.51</v>
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[10027,10],[20047,11],[30030,17],[40019,18]]</v>
       </c>
       <c r="H163">
         <v>2.51</v>
@@ -5143,7 +5143,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[10027,1],[10031,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[90039,2],[90040,3],[10037,4],[10032,5],[10027,10],[10031,11],[20047,12],[30030,17],[40019,18]]</v>
       </c>
       <c r="H164">
         <v>3.31</v>
@@ -5172,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="str">
-        <v>[[10037,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H165">
         <v>2.76</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[10027,10],[20047,11],[30030,17],[40019,18]]</v>
       </c>
       <c r="H166">
         <v>2.76</v>
@@ -5230,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[10027,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H167">
         <v>2.76</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[10027,5],[20047,10],[30030,11],[40019,18]]</v>
       </c>
       <c r="H168">
         <v>2.76</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[10027,10],[20047,11],[30030,17],[40019,18]]</v>
       </c>
       <c r="H169">
         <v>2.76</v>
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[10027,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H170">
         <v>2.76</v>
@@ -5346,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[10027,5],[20047,10],[30030,11],[40019,18]]</v>
       </c>
       <c r="H171">
         <v>2.76</v>
@@ -5375,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10032,4],[10027,10],[20047,11],[30030,17],[40019,18]]</v>
       </c>
       <c r="H172">
         <v>2.76</v>
@@ -5404,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="str">
-        <v>[[10037,1],[10032,1],[10027,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10032,3],[10027,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H173">
         <v>2.76</v>
@@ -5433,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="G174" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10032,1],[10027,1],[10045,1],[20047,1],[20027,1],[30030,1],[30023,1],[40019,1],[40017,1]]</v>
+        <v>[[90039,3],[90040,4],[10037,10],[10032,11],[10027,17],[10045,18],[20047,12],[20027,5],[30030,19],[30023,2],[40019,9],[40017,16]]</v>
       </c>
       <c r="H174">
         <v>3.64</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="str">
-        <v>[[10037,1],[10045,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[20047,5],[30030,10],[40019,11]]</v>
       </c>
       <c r="H175">
         <v>3.03</v>
@@ -5491,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10045,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H176">
         <v>3.03</v>
@@ -5520,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,5],[20047,10],[30030,11],[40019,18]]</v>
       </c>
       <c r="H177">
         <v>3.03</v>
@@ -5549,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,10],[20047,11],[30030,17],[40019,18]]</v>
       </c>
       <c r="H178">
         <v>3.03</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10045,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H179">
         <v>3.03</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,5],[20047,10],[30030,11],[40019,18]]</v>
       </c>
       <c r="H180">
         <v>3.03</v>
@@ -5636,7 +5636,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,10],[20047,11],[30030,17],[40019,18]]</v>
       </c>
       <c r="H181">
         <v>3.03</v>
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10045,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H182">
         <v>3.03</v>
@@ -5694,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,5],[20047,10],[30030,11],[40019,18]]</v>
       </c>
       <c r="H183">
         <v>3.03</v>
@@ -5723,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="G184" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10045,1],[10032,1],[10048,1],[20047,1],[20027,1],[30030,1],[30023,1],[40019,1],[40017,1]]</v>
+        <v>[[90039,3],[90040,4],[10037,10],[10045,11],[10032,17],[10048,18],[20047,12],[20027,5],[30030,19],[30023,2],[40019,9],[40017,16]]</v>
       </c>
       <c r="H184">
         <v>4</v>
@@ -5752,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="str">
-        <v>[[10037,1],[10045,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10045,3],[20047,4],[30030,10],[40019,11]]</v>
       </c>
       <c r="H185">
         <v>3.34</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="str">
-        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10048,5],[20047,10],[30030,11],[40019,18]]</v>
       </c>
       <c r="H186">
         <v>3.34</v>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="str">
-        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10048,10],[20047,11],[30030,17],[40019,18]]</v>
       </c>
       <c r="H187">
         <v>3.34</v>
@@ -5839,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="str">
-        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10045,3],[10048,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H188">
         <v>3.34</v>
@@ -5868,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="str">
-        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10048,5],[20047,10],[30030,11],[40019,18]]</v>
       </c>
       <c r="H189">
         <v>3.34</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="str">
-        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10048,10],[20047,11],[30030,17],[40019,18]]</v>
       </c>
       <c r="H190">
         <v>3.34</v>
@@ -5926,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="str">
-        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,2],[10045,3],[10048,4],[20047,10],[30030,11],[40019,17]]</v>
       </c>
       <c r="H191">
         <v>3.34</v>
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="str">
-        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[30030,1],[40019,1]]</v>
+        <v>[[10037,3],[10045,4],[10048,5],[20047,10],[30030,11],[40019,18]]</v>
       </c>
       <c r="H192">
         <v>3.34</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="str">
-        <v>[[10037,1],[10045,1],[10048,1],[20047,1],[20027,1],[30030,1],[30023,1],[40019,2]]</v>
+        <v>[[10037,2],[10045,3],[10048,4],[20047,5],[20027,10],[30030,11],[30023,17],[40019,18]]</v>
       </c>
       <c r="H193">
         <v>3.34</v>
@@ -6013,7 +6013,7 @@
         <v>1</v>
       </c>
       <c r="G194" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10045,1],[10048,1],[10042,1],[20047,1],[20027,1],[30030,1],[30023,1],[40019,1],[40027,1]]</v>
+        <v>[[90039,3],[90040,4],[10037,10],[10045,11],[10048,17],[10042,18],[20047,12],[20027,5],[30030,19],[30023,2],[40019,9],[40027,16]]</v>
       </c>
       <c r="H194">
         <v>4.4</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[20047,1],[30030,1],[40027,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,5],[20047,10],[30030,11],[40027,18]]</v>
       </c>
       <c r="H195">
         <v>3.67</v>
@@ -6071,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
+        <v>[[10037,2],[10045,3],[10032,4],[10027,5],[20047,10],[20027,11],[30030,12],[30023,17],[40027,18]]</v>
       </c>
       <c r="H196">
         <v>3.67</v>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="G197" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,10],[10027,11],[20047,17],[20027,18],[30030,12],[30023,5],[40027,19]]</v>
       </c>
       <c r="H197">
         <v>3.67</v>
@@ -6129,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="G198" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
+        <v>[[10037,2],[10045,3],[10032,4],[10027,5],[20047,10],[20027,11],[30030,12],[30023,17],[40027,18]]</v>
       </c>
       <c r="H198">
         <v>3.67</v>
@@ -6158,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,10],[10027,11],[20047,17],[20027,18],[30030,12],[30023,5],[40027,19]]</v>
       </c>
       <c r="H199">
         <v>3.67</v>
@@ -6187,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
+        <v>[[10037,2],[10045,3],[10032,4],[10027,5],[20047,10],[20027,11],[30030,12],[30023,17],[40027,18]]</v>
       </c>
       <c r="H200">
         <v>3.67</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,10],[10027,11],[20047,17],[20027,18],[30030,12],[30023,5],[40027,19]]</v>
       </c>
       <c r="H201">
         <v>3.67</v>
@@ -6245,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
+        <v>[[10037,2],[10045,3],[10032,4],[10027,5],[20047,10],[20027,11],[30030,12],[30023,17],[40027,18]]</v>
       </c>
       <c r="H202">
         <v>3.67</v>
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="str">
-        <v>[[10037,1],[10045,1],[10032,1],[10027,1],[20047,1],[20027,1],[30030,1],[30023,1],[40027,1]]</v>
+        <v>[[10037,3],[10045,4],[10032,10],[10027,11],[20047,17],[20027,18],[30030,12],[30023,5],[40027,19]]</v>
       </c>
       <c r="H203">
         <v>3.67</v>
@@ -6303,7 +6303,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="str">
-        <v>[[90039,1],[90040,1],[10037,1],[10045,1],[10032,1],[10027,1],[10048,1],[10042,1],[20047,1],[20027,1],[20043,1],[30030,1],[30023,1],[30025,1],[40027,1],[40032,1]]</v>
+        <v>[[90039,3],[90040,4],[10037,10],[10045,11],[10032,17],[10027,18],[10048,12],[10042,5],[20047,19],[20027,2],[20043,9],[30030,16],[30023,20],[30025,6],[40027,13],[40032,25]]</v>
       </c>
       <c r="H204">
         <v>5.65</v>

--- a/public/StageStepTable.xlsx
+++ b/public/StageStepTable.xlsx
@@ -532,7 +532,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10006,3],[20001,4],[30001,10],[40001,11]]</v>
       </c>
       <c r="H5">
         <v>0.6</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
+        <v>[[10002,2],[20002,3],[30005,4],[40002,10]]</v>
       </c>
       <c r="H6">
         <v>0.6</v>
@@ -590,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10008,3],[20003,4],[30002,5],[40003,11]]</v>
       </c>
       <c r="H7">
         <v>0.6</v>
@@ -619,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10012,3],[20012,4],[30006,10],[40008,11]]</v>
       </c>
       <c r="H8">
         <v>0.6</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
+        <v>[[10011,2],[20011,3],[30008,4],[40007,10]]</v>
       </c>
       <c r="H9">
         <v>0.6</v>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10009,3],[20004,4],[30003,5],[40003,11]]</v>
       </c>
       <c r="H10">
         <v>0.6</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10006,3],[20001,4],[30001,10],[40002,11]]</v>
       </c>
       <c r="H11">
         <v>0.6</v>
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="str">
-        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
+        <v>[[10002,2],[20002,3],[30005,4],[40004,10]]</v>
       </c>
       <c r="H12">
         <v>0.6</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10008,3],[20010,4],[30002,5],[40005,11]]</v>
       </c>
       <c r="H13">
         <v>0.6</v>
@@ -793,7 +793,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="str">
-        <v>[[90033,2],[90034,3],[10002,4],[20002,10],[30004,11],[40001,17]]</v>
+        <v>[[90033,2],[90034,3],[10012,4],[20005,10],[30006,11],[40008,17]]</v>
       </c>
       <c r="H14">
         <v>0.79</v>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="str">
-        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
+        <v>[[10011,2],[20009,3],[30008,4],[40007,10]]</v>
       </c>
       <c r="H15">
         <v>0.66</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10003,3],[20004,4],[30005,5],[40001,11]]</v>
       </c>
       <c r="H16">
         <v>0.66</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10006,3],[20010,4],[30001,10],[40002,11]]</v>
       </c>
       <c r="H17">
         <v>0.66</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="str">
-        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
+        <v>[[10002,2],[20005,3],[30002,4],[40006,10]]</v>
       </c>
       <c r="H18">
         <v>0.66</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10008,3],[20002,4],[30006,5],[40005,11]]</v>
       </c>
       <c r="H19">
         <v>0.66</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10012,3],[20008,4],[30005,10],[40008,11]]</v>
       </c>
       <c r="H20">
         <v>0.66</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
+        <v>[[10011,2],[20009,3],[30003,4],[40003,10]]</v>
       </c>
       <c r="H21">
         <v>0.66</v>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10003,3],[20010,4],[30001,5],[40001,11]]</v>
       </c>
       <c r="H22">
         <v>0.66</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10006,3],[20005,4],[30007,10],[40007,11]]</v>
       </c>
       <c r="H23">
         <v>0.66</v>
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="str">
-        <v>[[90033,2],[90034,3],[10002,4],[10009,10],[20002,11],[30004,17],[40001,18]]</v>
+        <v>[[90033,2],[90034,3],[10002,4],[10009,10],[20004,11],[30002,17],[40004,18]]</v>
       </c>
       <c r="H24">
         <v>0.87</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10008,3],[20002,4],[30006,5],[40002,11]]</v>
       </c>
       <c r="H25">
         <v>0.73</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10012,3],[20010,4],[30005,10],[40003,11]]</v>
       </c>
       <c r="H26">
         <v>0.73</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="str">
-        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
+        <v>[[10011,2],[20009,3],[30003,4],[40008,10]]</v>
       </c>
       <c r="H27">
         <v>0.73</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10022,3],[20005,4],[30001,5],[40005,11]]</v>
       </c>
       <c r="H28">
         <v>0.73</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10006,3],[20012,4],[30007,10],[40007,11]]</v>
       </c>
       <c r="H29">
         <v>0.73</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="str">
-        <v>[[10002,2],[20002,3],[30004,4],[40001,10]]</v>
+        <v>[[10020,2],[20004,3],[30002,4],[40004,10]]</v>
       </c>
       <c r="H30">
         <v>0.73</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="str">
-        <v>[[10002,3],[20002,4],[30004,5],[40001,11]]</v>
+        <v>[[10008,3],[20002,4],[30006,5],[40003,11]]</v>
       </c>
       <c r="H31">
         <v>0.73</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10012,3],[20010,4],[30005,10],[40002,11]]</v>
       </c>
       <c r="H32">
         <v>0.73</v>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="str">
-        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
+        <v>[[10011,2],[20009,3],[30003,4],[40008,10]]</v>
       </c>
       <c r="H33">
         <v>0.73</v>
@@ -1373,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="str">
-        <v>[[90035,2],[90036,3],[10002,4],[10009,10],[20002,11],[30004,17],[40001,18]]</v>
+        <v>[[90035,3],[90036,4],[10022,10],[20005,11],[30001,17],[40005,18]]</v>
       </c>
       <c r="H34">
         <v>0.96</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="str">
-        <v>[[10002,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10006,3],[20008,4],[30008,10],[40016,11]]</v>
       </c>
       <c r="H35">
         <v>0.8</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="str">
-        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
+        <v>[[10020,2],[20004,3],[30002,4],[40007,10]]</v>
       </c>
       <c r="H36">
         <v>0.8</v>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="str">
-        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
+        <v>[[10008,3],[10002,4],[20002,5],[30006,10],[40003,11]]</v>
       </c>
       <c r="H37">
         <v>0.8</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="str">
-        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10024,3],[20010,4],[30005,10],[40002,11]]</v>
       </c>
       <c r="H38">
         <v>0.8</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="str">
-        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
+        <v>[[10012,2],[20009,3],[30003,4],[40008,10]]</v>
       </c>
       <c r="H39">
         <v>0.8</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="str">
-        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
+        <v>[[10022,3],[20005,4],[30001,5],[40004,11]]</v>
       </c>
       <c r="H40">
         <v>0.8</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="str">
-        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10006,2],[10009,3],[20008,4],[30008,10],[40005,11]]</v>
       </c>
       <c r="H41">
         <v>0.8</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="str">
-        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
+        <v>[[10020,2],[20004,3],[30002,4],[40007,10]]</v>
       </c>
       <c r="H42">
         <v>0.8</v>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="str">
-        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
+        <v>[[10014,3],[20002,4],[30006,5],[40003,11]]</v>
       </c>
       <c r="H43">
         <v>0.8</v>
@@ -1663,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="str">
-        <v>[[90035,3],[90036,4],[10002,10],[10009,11],[10012,17],[20002,18],[30004,12],[40001,5]]</v>
+        <v>[[90035,2],[90036,3],[10019,4],[20010,10],[30005,11],[40002,17]]</v>
       </c>
       <c r="H44">
         <v>1.05</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="str">
-        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
+        <v>[[10008,2],[20009,3],[30003,4],[40008,10]]</v>
       </c>
       <c r="H45">
         <v>0.88</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="str">
-        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
+        <v>[[10022,3],[20005,4],[30001,5],[40004,11]]</v>
       </c>
       <c r="H46">
         <v>0.88</v>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="str">
-        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10018,3],[20012,4],[30008,10],[40005,11]]</v>
       </c>
       <c r="H47">
         <v>0.88</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="str">
-        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
+        <v>[[10020,2],[20004,3],[30002,4],[40007,10]]</v>
       </c>
       <c r="H48">
         <v>0.88</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="str">
-        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
+        <v>[[10014,3],[20002,4],[30006,5],[40003,11]]</v>
       </c>
       <c r="H49">
         <v>0.88</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="str">
-        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10019,3],[20010,4],[30005,10],[40002,11]]</v>
       </c>
       <c r="H50">
         <v>0.88</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="str">
-        <v>[[10002,3],[10009,4],[20002,10],[30004,11],[40001,17]]</v>
+        <v>[[10015,2],[20009,3],[30003,4],[40008,10]]</v>
       </c>
       <c r="H51">
         <v>0.88</v>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="str">
-        <v>[[10002,3],[10009,4],[20002,5],[30004,10],[40001,11]]</v>
+        <v>[[10022,3],[20005,4],[30001,5],[40004,11]]</v>
       </c>
       <c r="H52">
         <v>0.88</v>
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="str">
-        <v>[[10002,2],[10009,3],[20002,4],[30004,10],[40001,11]]</v>
+        <v>[[10018,3],[20012,4],[30008,10],[40005,11]]</v>
       </c>
       <c r="H53">
         <v>0.88</v>
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="str">
-        <v>[[90035,3],[90036,4],[10002,10],[10009,11],[10014,17],[20002,18],[20004,12],[30004,5],[30007,19],[40001,2]]</v>
+        <v>[[90035,2],[90036,3],[10020,4],[10013,10],[20014,11],[30002,17],[40007,18]]</v>
       </c>
       <c r="H54">
         <v>1.35</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="str">
-        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
+        <v>[[10028,3],[20015,4],[30014,5],[40016,11]]</v>
       </c>
       <c r="H55">
         <v>0.97</v>
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="str">
-        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10031,3],[20020,4],[30013,10],[40015,11]]</v>
       </c>
       <c r="H56">
         <v>0.97</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="str">
-        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
+        <v>[[10014,2],[20023,3],[30009,4],[40014,10]]</v>
       </c>
       <c r="H57">
         <v>0.97</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="str">
-        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
+        <v>[[10036,3],[20018,4],[30016,5],[40009,11]]</v>
       </c>
       <c r="H58">
         <v>0.97</v>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="str">
-        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10022,3],[20014,4],[30011,10],[40012,11]]</v>
       </c>
       <c r="H59">
         <v>0.97</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="str">
-        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
+        <v>[[10020,2],[20015,3],[30012,4],[40013,10]]</v>
       </c>
       <c r="H60">
         <v>0.97</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="str">
-        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
+        <v>[[10028,3],[20020,4],[30014,5],[40016,11]]</v>
       </c>
       <c r="H61">
         <v>0.97</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="str">
-        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10031,3],[20023,4],[30013,10],[40015,11]]</v>
       </c>
       <c r="H62">
         <v>0.97</v>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="str">
-        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
+        <v>[[10014,2],[20024,3],[30009,4],[40018,10]]</v>
       </c>
       <c r="H63">
         <v>0.97</v>
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="G64" t="str">
-        <v>[[90037,2],[90038,3],[10014,4],[10022,10],[20014,11],[30014,17],[40014,18]]</v>
+        <v>[[90037,3],[90038,4],[10036,10],[20018,11],[30016,17],[40009,18]]</v>
       </c>
       <c r="H64">
         <v>1.28</v>
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="str">
-        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10022,3],[20014,4],[30019,10],[40021,11]]</v>
       </c>
       <c r="H65">
         <v>1.06</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="str">
-        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
+        <v>[[10020,2],[20015,3],[30011,4],[40012,10]]</v>
       </c>
       <c r="H66">
         <v>1.06</v>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="str">
-        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
+        <v>[[10028,3],[20020,4],[30014,5],[40017,11]]</v>
       </c>
       <c r="H67">
         <v>1.06</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="str">
-        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10031,3],[20023,4],[30013,10],[40024,11]]</v>
       </c>
       <c r="H68">
         <v>1.06</v>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="str">
-        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
+        <v>[[10027,2],[20024,3],[30009,4],[40022,10]]</v>
       </c>
       <c r="H69">
         <v>1.06</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="str">
-        <v>[[10014,3],[20014,4],[30014,5],[40014,11]]</v>
+        <v>[[10036,3],[20018,4],[30016,5],[40023,11]]</v>
       </c>
       <c r="H70">
         <v>1.06</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="str">
-        <v>[[10014,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10022,3],[20014,4],[30012,10],[40018,11]]</v>
       </c>
       <c r="H71">
         <v>1.06</v>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="str">
-        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
+        <v>[[10020,2],[20015,3],[30011,4],[40012,10]]</v>
       </c>
       <c r="H72">
         <v>1.06</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="str">
-        <v>[[10014,3],[10022,4],[20014,5],[30014,10],[40014,11]]</v>
+        <v>[[10028,3],[20020,4],[30014,5],[40009,11]]</v>
       </c>
       <c r="H73">
         <v>1.06</v>
@@ -2533,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="str">
-        <v>[[90037,2],[90038,3],[10014,4],[10022,10],[20014,11],[30014,17],[40014,18]]</v>
+        <v>[[90037,2],[90038,3],[10031,4],[20023,10],[30013,11],[40016,17]]</v>
       </c>
       <c r="H74">
         <v>1.4</v>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="str">
-        <v>[[10014,2],[20014,3],[30014,4],[40014,10]]</v>
+        <v>[[10027,2],[20014,3],[30010,4],[40017,10]]</v>
       </c>
       <c r="H75">
         <v>1.17</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="str">
-        <v>[[10014,3],[10022,4],[20014,5],[30014,10],[40014,11]]</v>
+        <v>[[10036,3],[20018,4],[30016,5],[40014,11]]</v>
       </c>
       <c r="H76">
         <v>1.17</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="str">
-        <v>[[10014,2],[10022,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10034,3],[20015,4],[30009,10],[40012,11]]</v>
       </c>
       <c r="H77">
         <v>1.17</v>
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="str">
-        <v>[[10014,3],[10022,4],[20014,10],[30014,11],[40014,17]]</v>
+        <v>[[10022,3],[10020,4],[20024,10],[30011,11],[40011,17]]</v>
       </c>
       <c r="H78">
         <v>1.17</v>
@@ -2678,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="str">
-        <v>[[10014,3],[10022,4],[20014,5],[30014,10],[40014,11]]</v>
+        <v>[[10028,3],[20020,4],[30014,5],[40009,11]]</v>
       </c>
       <c r="H79">
         <v>1.17</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="str">
-        <v>[[10014,2],[10022,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10031,3],[20023,4],[30013,10],[40016,11]]</v>
       </c>
       <c r="H80">
         <v>1.17</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="str">
-        <v>[[10014,3],[10022,4],[20014,10],[30014,11],[40014,17]]</v>
+        <v>[[10027,2],[20014,3],[30012,4],[40015,10]]</v>
       </c>
       <c r="H81">
         <v>1.17</v>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="str">
-        <v>[[10014,3],[10022,4],[20014,5],[30014,10],[40014,11]]</v>
+        <v>[[10036,3],[20018,4],[30016,5],[40014,11]]</v>
       </c>
       <c r="H82">
         <v>1.17</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="str">
-        <v>[[10014,2],[10022,3],[20014,4],[30014,10],[40014,11]]</v>
+        <v>[[10034,3],[20015,4],[30009,10],[40012,11]]</v>
       </c>
       <c r="H83">
         <v>1.17</v>
@@ -2823,7 +2823,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="str">
-        <v>[[90037,3],[90038,4],[10014,10],[10022,11],[10017,17],[20014,18],[30014,12],[40014,5]]</v>
+        <v>[[90037,3],[90038,4],[10032,5],[20033,10],[30011,11],[40011,18]]</v>
       </c>
       <c r="H84">
         <v>1.54</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10028,3],[20028,4],[30024,5],[40024,11]]</v>
       </c>
       <c r="H85">
         <v>1.29</v>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20030,4],[30023,10],[40023,11]]</v>
       </c>
       <c r="H86">
         <v>1.29</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20026,3],[30018,4],[40017,10]]</v>
       </c>
       <c r="H87">
         <v>1.29</v>
@@ -2939,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10031,3],[20036,4],[30019,5],[40018,11]]</v>
       </c>
       <c r="H88">
         <v>1.29</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10036,3],[20033,4],[30022,10],[40022,11]]</v>
       </c>
       <c r="H89">
         <v>1.29</v>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10037,2],[20028,3],[30024,4],[40019,10]]</v>
       </c>
       <c r="H90">
         <v>1.29</v>
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10028,3],[20030,4],[30023,5],[40024,11]]</v>
       </c>
       <c r="H91">
         <v>1.29</v>
@@ -3055,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20026,4],[30018,10],[40020,11]]</v>
       </c>
       <c r="H92">
         <v>1.29</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20033,3],[30020,4],[40017,10]]</v>
       </c>
       <c r="H93">
         <v>1.29</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="G94" t="str">
-        <v>[[90039,3],[90040,4],[10037,10],[20027,11],[30023,17],[40019,18]]</v>
+        <v>[[90039,3],[90040,4],[10043,10],[20036,11],[30019,17],[40018,18]]</v>
       </c>
       <c r="H94">
         <v>1.7</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10031,3],[20028,4],[30024,10],[40021,11]]</v>
       </c>
       <c r="H95">
         <v>1.41</v>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10037,2],[20030,3],[30022,4],[40019,10]]</v>
       </c>
       <c r="H96">
         <v>1.41</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10041,3],[20027,4],[30023,5],[40024,11]]</v>
       </c>
       <c r="H97">
         <v>1.41</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20026,4],[30018,10],[40023,11]]</v>
       </c>
       <c r="H98">
         <v>1.41</v>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20033,3],[30020,4],[40017,10]]</v>
       </c>
       <c r="H99">
         <v>1.41</v>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10043,3],[20036,4],[30019,5],[40018,11]]</v>
       </c>
       <c r="H100">
         <v>1.41</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10028,3],[20028,4],[30024,10],[40021,11]]</v>
       </c>
       <c r="H101">
         <v>1.41</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10037,2],[20030,3],[30022,4],[40019,10]]</v>
       </c>
       <c r="H102">
         <v>1.41</v>
@@ -3374,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10041,3],[20027,4],[30023,5],[40022,11]]</v>
       </c>
       <c r="H103">
         <v>1.41</v>
@@ -3403,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="G104" t="str">
-        <v>[[90039,2],[90040,3],[10037,4],[10032,10],[20027,11],[30023,17],[40019,18]]</v>
+        <v>[[90039,2],[90040,3],[10047,4],[20026,10],[30031,11],[40020,17]]</v>
       </c>
       <c r="H104">
         <v>2.18</v>
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20033,3],[30018,4],[40024,10]]</v>
       </c>
       <c r="H105">
         <v>1.56</v>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10043,3],[20036,4],[30019,5],[40018,11]]</v>
       </c>
       <c r="H106">
         <v>1.56</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10042,3],[20028,4],[30024,10],[40017,11]]</v>
       </c>
       <c r="H107">
         <v>1.56</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10037,2],[20030,3],[30022,4],[40019,10]]</v>
       </c>
       <c r="H108">
         <v>1.56</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10041,3],[20027,4],[30023,5],[40021,11]]</v>
       </c>
       <c r="H109">
         <v>1.56</v>
@@ -3577,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20026,4],[30020,10],[40022,11]]</v>
       </c>
       <c r="H110">
         <v>1.56</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20033,3],[30018,4],[40020,10]]</v>
       </c>
       <c r="H111">
         <v>1.56</v>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10043,3],[20036,4],[30019,5],[40018,11]]</v>
       </c>
       <c r="H112">
         <v>1.56</v>
@@ -3664,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10042,3],[20028,4],[30024,10],[40017,11]]</v>
       </c>
       <c r="H113">
         <v>1.56</v>
@@ -3693,7 +3693,7 @@
         <v>1</v>
       </c>
       <c r="G114" t="str">
-        <v>[[90039,2],[90040,3],[10037,4],[10032,10],[20027,11],[30023,17],[40019,18]]</v>
+        <v>[[90039,3],[90040,4],[10037,5],[20030,10],[30031,11],[40024,18]]</v>
       </c>
       <c r="H114">
         <v>2.05</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10041,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H115">
         <v>1.71</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20026,4],[30022,10],[40021,11]]</v>
       </c>
       <c r="H116">
         <v>1.71</v>
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20033,3],[30018,4],[40022,10]]</v>
       </c>
       <c r="H117">
         <v>1.71</v>
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10043,3],[20036,4],[30019,5],[40018,11]]</v>
       </c>
       <c r="H118">
         <v>1.71</v>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10042,3],[20028,4],[30024,10],[40017,11]]</v>
       </c>
       <c r="H119">
         <v>1.71</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10037,2],[20030,3],[30020,4],[40020,10]]</v>
       </c>
       <c r="H120">
         <v>1.71</v>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10041,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H121">
         <v>1.71</v>
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20026,4],[30022,10],[40021,11]]</v>
       </c>
       <c r="H122">
         <v>1.71</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20033,3],[30018,4],[40022,10]]</v>
       </c>
       <c r="H123">
         <v>1.71</v>
@@ -3983,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="G124" t="str">
-        <v>[[90039,2],[90040,3],[10037,4],[10045,10],[20027,11],[30023,17],[40019,18]]</v>
+        <v>[[90039,3],[90040,4],[10043,10],[20036,11],[30031,17],[40018,18]]</v>
       </c>
       <c r="H124">
         <v>2.26</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10042,3],[20028,4],[30024,10],[40017,11]]</v>
       </c>
       <c r="H125">
         <v>1.88</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10037,2],[20030,3],[30019,4],[40020,10]]</v>
       </c>
       <c r="H126">
         <v>1.88</v>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10041,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H127">
         <v>1.88</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20026,4],[30022,10],[40021,11]]</v>
       </c>
       <c r="H128">
         <v>1.88</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20033,3],[30018,4],[40022,10]]</v>
       </c>
       <c r="H129">
         <v>1.88</v>
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="str">
-        <v>[[10037,3],[20027,4],[30023,5],[40019,11]]</v>
+        <v>[[10043,3],[20036,4],[30031,5],[40018,11]]</v>
       </c>
       <c r="H130">
         <v>1.88</v>
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="str">
-        <v>[[10037,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10042,3],[20028,4],[30024,10],[40017,11]]</v>
       </c>
       <c r="H131">
         <v>1.88</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10037,2],[20030,3],[30019,4],[40020,10]]</v>
       </c>
       <c r="H132">
         <v>1.88</v>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="str">
-        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
+        <v>[[10041,3],[20027,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H133">
         <v>1.88</v>
@@ -4273,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="str">
-        <v>[[90039,2],[90040,3],[10037,4],[10032,10],[20027,11],[30023,17],[40019,18]]</v>
+        <v>[[90039,2],[90040,3],[10047,4],[10038,10],[20046,11],[30029,17],[40021,18]]</v>
       </c>
       <c r="H134">
         <v>2.49</v>
@@ -4302,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="str">
-        <v>[[10037,2],[20027,3],[30023,4],[40019,10]]</v>
+        <v>[[10039,2],[20033,3],[30018,4],[40022,10]]</v>
       </c>
       <c r="H135">
         <v>2.07</v>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="str">
-        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
+        <v>[[10043,3],[20041,4],[30031,5],[40018,11]]</v>
       </c>
       <c r="H136">
         <v>2.07</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="str">
-        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10042,3],[20028,4],[30024,10],[40017,11]]</v>
       </c>
       <c r="H137">
         <v>2.07</v>
@@ -4389,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="str">
-        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
+        <v>[[10037,2],[20030,3],[30019,4],[40020,10]]</v>
       </c>
       <c r="H138">
         <v>2.07</v>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="str">
-        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
+        <v>[[10041,3],[20026,4],[30023,5],[40019,11]]</v>
       </c>
       <c r="H139">
         <v>2.07</v>
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="str">
-        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20046,4],[30022,10],[40021,11]]</v>
       </c>
       <c r="H140">
         <v>2.07</v>
@@ -4476,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="str">
-        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
+        <v>[[10039,2],[20033,3],[30018,4],[40022,10]]</v>
       </c>
       <c r="H141">
         <v>2.07</v>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="str">
-        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
+        <v>[[10031,3],[10028,4],[20041,5],[30017,10],[40018,11]]</v>
       </c>
       <c r="H142">
         <v>2.07</v>
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="str">
-        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10043,3],[20028,4],[30031,10],[40017,11]]</v>
       </c>
       <c r="H143">
         <v>2.07</v>
@@ -4563,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="str">
-        <v>[[90039,3],[90040,4],[10037,10],[10032,11],[10027,17],[20027,18],[30023,12],[40019,5]]</v>
+        <v>[[90039,2],[90040,3],[10037,4],[10042,10],[20043,11],[30029,17],[40029,18]]</v>
       </c>
       <c r="H144">
         <v>2.73</v>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="str">
-        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
+        <v>[[10041,3],[20030,4],[30024,5],[40019,11]]</v>
       </c>
       <c r="H145">
         <v>2.28</v>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="str">
-        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,3],[20046,4],[30023,10],[40021,11]]</v>
       </c>
       <c r="H146">
         <v>2.28</v>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="str">
-        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
+        <v>[[10039,2],[20033,3],[30018,4],[40022,10]]</v>
       </c>
       <c r="H147">
         <v>2.28</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="str">
-        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
+        <v>[[10038,3],[20041,4],[30019,5],[40018,11]]</v>
       </c>
       <c r="H148">
         <v>2.28</v>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="str">
-        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10043,3],[20028,4],[30031,10],[40017,11]]</v>
       </c>
       <c r="H149">
         <v>2.28</v>
@@ -4737,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="str">
-        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
+        <v>[[10037,2],[20043,3],[30029,4],[40020,10]]</v>
       </c>
       <c r="H150">
         <v>2.28</v>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="str">
-        <v>[[10037,3],[10032,4],[20027,5],[30023,10],[40019,11]]</v>
+        <v>[[10041,3],[20030,4],[30024,5],[40019,11]]</v>
       </c>
       <c r="H151">
         <v>2.28</v>
@@ -4795,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="str">
-        <v>[[10037,2],[10032,3],[20027,4],[30023,10],[40019,11]]</v>
+        <v>[[10047,2],[10042,3],[20046,4],[30023,10],[40021,11]]</v>
       </c>
       <c r="H152">
         <v>2.28</v>
@@ -4824,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="str">
-        <v>[[10037,3],[10032,4],[20027,10],[30023,11],[40019,17]]</v>
+        <v>[[10039,3],[10040,4],[20033,10],[30028,11],[40022,17]]</v>
       </c>
       <c r="H153">
         <v>2.28</v>
@@ -4853,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="str">
-        <v>[[90039,3],[90040,4],[10037,10],[10032,11],[10045,17],[10027,18],[20027,12],[20047,5],[30023,19],[30030,2],[40019,9]]</v>
+        <v>[[90039,2],[90040,3],[10038,4],[10046,10],[20041,11],[30032,17],[40029,18]]</v>
       </c>
       <c r="H154">
         <v>3.51</v>
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="str">
-        <v>[[10037,2],[10032,3],[20047,4],[30030,10],[40019,11]]</v>
+        <v>[[10043,3],[20028,4],[30031,10],[40018,11]]</v>
       </c>
       <c r="H155">
         <v>2.51</v>
@@ -4911,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="str">
-        <v>[[10037,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10037,3],[10044,4],[20043,10],[30029,11],[40017,17]]</v>
       </c>
       <c r="H156">
         <v>2.51</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="str">
-        <v>[[10037,3],[10032,4],[20047,5],[30030,10],[40019,11]]</v>
+        <v>[[10041,3],[20037,4],[30024,5],[40019,11]]</v>
       </c>
       <c r="H157">
         <v>2.51</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="str">
-        <v>[[10037,2],[10032,3],[20047,4],[30030,10],[40019,11]]</v>
+        <v>[[10047,2],[10042,3],[20046,4],[30023,10],[40021,11]]</v>
       </c>
       <c r="H158">
         <v>2.51</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="str">
-        <v>[[10037,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10039,3],[10040,4],[20040,10],[30028,11],[40022,17]]</v>
       </c>
       <c r="H159">
         <v>2.51</v>
@@ -5027,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="str">
-        <v>[[10037,3],[10032,4],[20047,5],[30030,10],[40019,11]]</v>
+        <v>[[10038,3],[10046,4],[20041,5],[30018,10],[40020,11]]</v>
       </c>
       <c r="H160">
         <v>2.51</v>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="str">
-        <v>[[10037,2],[10032,3],[20047,4],[30030,10],[40019,11]]</v>
+        <v>[[10043,2],[10048,3],[20028,4],[30031,10],[40018,11]]</v>
       </c>
       <c r="H161">
         <v>2.51</v>
@@ -5085,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="str">
-        <v>[[10037,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10037,3],[10044,4],[20043,10],[30029,11],[40017,17]]</v>
       </c>
       <c r="H162">
         <v>2.51</v>
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="str">
-        <v>[[10037,3],[10032,4],[10027,10],[20047,11],[30030,17],[40019,18]]</v>
+        <v>[[10041,3],[10045,4],[20037,5],[30024,10],[40019,11]]</v>
       </c>
       <c r="H163">
         <v>2.51</v>
@@ -5143,7 +5143,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="str">
-        <v>[[90039,2],[90040,3],[10037,4],[10032,5],[10027,10],[10031,11],[20047,12],[30030,17],[40019,18]]</v>
+        <v>[[90039,3],[90040,4],[10047,10],[10042,11],[10028,17],[20046,18],[30032,12],[40029,5]]</v>
       </c>
       <c r="H164">
         <v>3.31</v>
@@ -5172,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="str">
-        <v>[[10037,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10039,3],[10040,4],[20033,10],[30023,11],[40021,17]]</v>
       </c>
       <c r="H165">
         <v>2.76</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="str">
-        <v>[[10037,3],[10032,4],[10027,10],[20047,11],[30030,17],[40019,18]]</v>
+        <v>[[10038,3],[10046,4],[20041,5],[30028,10],[40025,11]]</v>
       </c>
       <c r="H166">
         <v>2.76</v>
@@ -5230,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="str">
-        <v>[[10037,2],[10032,3],[10027,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10043,2],[10048,3],[20040,4],[30031,10],[40018,11]]</v>
       </c>
       <c r="H167">
         <v>2.76</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="str">
-        <v>[[10037,3],[10032,4],[10027,5],[20047,10],[30030,11],[40019,18]]</v>
+        <v>[[10037,3],[10044,4],[20043,10],[30029,11],[40032,17]]</v>
       </c>
       <c r="H168">
         <v>2.76</v>
@@ -5288,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="str">
-        <v>[[10037,3],[10032,4],[10027,10],[20047,11],[30030,17],[40019,18]]</v>
+        <v>[[10041,3],[10045,4],[20037,5],[30024,10],[40019,11]]</v>
       </c>
       <c r="H169">
         <v>2.76</v>
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="str">
-        <v>[[10037,2],[10032,3],[10027,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10047,2],[10042,3],[20046,4],[30018,10],[40029,11]]</v>
       </c>
       <c r="H170">
         <v>2.76</v>
@@ -5346,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="str">
-        <v>[[10037,3],[10032,4],[10027,5],[20047,10],[30030,11],[40019,18]]</v>
+        <v>[[10039,3],[10040,4],[20038,10],[30023,11],[40021,17]]</v>
       </c>
       <c r="H171">
         <v>2.76</v>
@@ -5375,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="str">
-        <v>[[10037,3],[10032,4],[10027,10],[20047,11],[30030,17],[40019,18]]</v>
+        <v>[[10038,3],[10046,4],[20041,5],[30028,10],[40025,11]]</v>
       </c>
       <c r="H172">
         <v>2.76</v>
@@ -5404,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="str">
-        <v>[[10037,2],[10032,3],[10027,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10043,2],[10048,3],[20040,4],[30031,10],[40026,11]]</v>
       </c>
       <c r="H173">
         <v>2.76</v>
@@ -5433,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="G174" t="str">
-        <v>[[90039,3],[90040,4],[10037,10],[10032,11],[10027,17],[10045,18],[20047,12],[20027,5],[30030,19],[30023,2],[40019,9],[40017,16]]</v>
+        <v>[[90039,3],[90040,4],[10037,10],[10044,11],[10041,17],[20043,18],[30029,12],[40032,5]]</v>
       </c>
       <c r="H174">
         <v>3.64</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="str">
-        <v>[[10037,3],[10045,4],[20047,5],[30030,10],[40019,11]]</v>
+        <v>[[10045,3],[10031,4],[20037,5],[30024,10],[40019,11]]</v>
       </c>
       <c r="H175">
         <v>3.03</v>
@@ -5491,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="str">
-        <v>[[10037,2],[10045,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10047,2],[10042,3],[10028,4],[20046,10],[30032,11],[40029,17]]</v>
       </c>
       <c r="H176">
         <v>3.03</v>
@@ -5520,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="str">
-        <v>[[10037,3],[10045,4],[10032,5],[20047,10],[30030,11],[40019,18]]</v>
+        <v>[[10039,3],[10040,4],[20038,10],[30026,11],[40018,17]]</v>
       </c>
       <c r="H177">
         <v>3.03</v>
@@ -5549,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="str">
-        <v>[[10037,3],[10045,4],[10032,10],[20047,11],[30030,17],[40019,18]]</v>
+        <v>[[10038,3],[10046,4],[20041,5],[30028,10],[40025,11]]</v>
       </c>
       <c r="H178">
         <v>3.03</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="str">
-        <v>[[10037,2],[10045,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10043,2],[10048,3],[20040,4],[30018,10],[40026,11]]</v>
       </c>
       <c r="H179">
         <v>3.03</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="str">
-        <v>[[10037,3],[10045,4],[10032,5],[20047,10],[30030,11],[40019,18]]</v>
+        <v>[[10041,3],[10037,4],[20043,10],[30031,11],[40032,17]]</v>
       </c>
       <c r="H180">
         <v>3.03</v>
@@ -5636,7 +5636,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="str">
-        <v>[[10037,3],[10045,4],[10032,10],[20047,11],[30030,17],[40019,18]]</v>
+        <v>[[10044,3],[10045,4],[20037,5],[30029,10],[40019,11]]</v>
       </c>
       <c r="H181">
         <v>3.03</v>
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="str">
-        <v>[[10037,2],[10045,3],[10032,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10047,2],[10042,3],[10028,4],[20046,10],[30032,11],[40029,17]]</v>
       </c>
       <c r="H182">
         <v>3.03</v>
@@ -5694,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="str">
-        <v>[[10037,3],[10045,4],[10032,5],[20047,10],[30030,11],[40019,18]]</v>
+        <v>[[10039,3],[10040,4],[10031,5],[20038,10],[30026,11],[40018,18]]</v>
       </c>
       <c r="H183">
         <v>3.03</v>
@@ -5723,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="G184" t="str">
-        <v>[[90039,3],[90040,4],[10037,10],[10045,11],[10032,17],[10048,18],[20047,12],[20027,5],[30030,19],[30023,2],[40019,9],[40017,16]]</v>
+        <v>[[90039,3],[90040,4],[10038,10],[10046,11],[10043,17],[20041,18],[30028,12],[40025,5]]</v>
       </c>
       <c r="H184">
         <v>4</v>
@@ -5752,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="str">
-        <v>[[10037,2],[10045,3],[20047,4],[30030,10],[40019,11]]</v>
+        <v>[[10048,2],[10036,3],[20040,4],[30024,10],[40017,11]]</v>
       </c>
       <c r="H185">
         <v>3.34</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="str">
-        <v>[[10037,3],[10045,4],[10048,5],[20047,10],[30030,11],[40019,18]]</v>
+        <v>[[10037,3],[10041,4],[10027,5],[20043,10],[30031,11],[40032,18]]</v>
       </c>
       <c r="H186">
         <v>3.34</v>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="str">
-        <v>[[10037,3],[10045,4],[10048,10],[20047,11],[30030,17],[40019,18]]</v>
+        <v>[[10044,3],[10045,4],[20037,5],[30029,10],[40026,11]]</v>
       </c>
       <c r="H187">
         <v>3.34</v>
@@ -5839,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="str">
-        <v>[[10037,2],[10045,3],[10048,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10047,2],[10042,3],[10039,4],[20046,10],[30032,11],[40029,17]]</v>
       </c>
       <c r="H188">
         <v>3.34</v>
@@ -5868,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="str">
-        <v>[[10037,3],[10045,4],[10048,5],[20047,10],[30030,11],[40019,18]]</v>
+        <v>[[10040,3],[10031,4],[10028,5],[20038,10],[30026,11],[40030,18]]</v>
       </c>
       <c r="H189">
         <v>3.34</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="str">
-        <v>[[10037,3],[10045,4],[10048,10],[20047,11],[30030,17],[40019,18]]</v>
+        <v>[[10043,3],[10038,4],[20041,5],[30028,10],[40025,11]]</v>
       </c>
       <c r="H190">
         <v>3.34</v>
@@ -5926,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="str">
-        <v>[[10037,2],[10045,3],[10048,4],[20047,10],[30030,11],[40019,17]]</v>
+        <v>[[10046,2],[10048,3],[10036,4],[20040,10],[30025,11],[40018,17]]</v>
       </c>
       <c r="H191">
         <v>3.34</v>
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="str">
-        <v>[[10037,3],[10045,4],[10048,5],[20047,10],[30030,11],[40019,18]]</v>
+        <v>[[10041,3],[10037,4],[10034,5],[20043,10],[30031,11],[40032,18]]</v>
       </c>
       <c r="H192">
         <v>3.34</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="str">
-        <v>[[10037,2],[10045,3],[10048,4],[20047,5],[20027,10],[30030,11],[30023,17],[40019,18]]</v>
+        <v>[[10044,3],[10045,4],[10047,10],[20037,11],[30029,17],[40026,18]]</v>
       </c>
       <c r="H193">
         <v>3.34</v>
@@ -6013,7 +6013,7 @@
         <v>1</v>
       </c>
       <c r="G194" t="str">
-        <v>[[90039,3],[90040,4],[10037,10],[10045,11],[10048,17],[10042,18],[20047,12],[20027,5],[30030,19],[30023,2],[40019,9],[40027,16]]</v>
+        <v>[[90039,2],[90040,3],[10039,4],[10042,5],[10040,10],[20046,11],[20039,12],[30032,17],[40029,18]]</v>
       </c>
       <c r="H194">
         <v>4.4</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="str">
-        <v>[[10037,3],[10045,4],[10032,5],[20047,10],[30030,11],[40027,18]]</v>
+        <v>[[10031,3],[10028,4],[10043,5],[20038,10],[30026,11],[40019,18]]</v>
       </c>
       <c r="H195">
         <v>3.67</v>
@@ -6071,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="str">
-        <v>[[10037,2],[10045,3],[10032,4],[10027,5],[20047,10],[20027,11],[30030,12],[30023,17],[40027,18]]</v>
+        <v>[[10038,3],[10046,4],[10027,10],[20041,11],[30028,17],[40025,18]]</v>
       </c>
       <c r="H196">
         <v>3.67</v>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="G197" t="str">
-        <v>[[10037,3],[10045,4],[10032,10],[10027,11],[20047,17],[20027,18],[30030,12],[30023,5],[40027,19]]</v>
+        <v>[[10048,2],[10041,3],[10037,4],[20040,10],[30025,11],[40030,17]]</v>
       </c>
       <c r="H197">
         <v>3.67</v>
@@ -6129,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="G198" t="str">
-        <v>[[10037,2],[10045,3],[10032,4],[10027,5],[20047,10],[20027,11],[30030,12],[30023,17],[40027,18]]</v>
+        <v>[[10047,3],[10036,4],[10034,5],[20043,10],[30031,11],[40032,18]]</v>
       </c>
       <c r="H198">
         <v>3.67</v>
@@ -6158,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="str">
-        <v>[[10037,3],[10045,4],[10032,10],[10027,11],[20047,17],[20027,18],[30030,12],[30023,5],[40027,19]]</v>
+        <v>[[10044,3],[10045,4],[10039,10],[20037,11],[30029,17],[40026,18]]</v>
       </c>
       <c r="H199">
         <v>3.67</v>
@@ -6187,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="str">
-        <v>[[10037,2],[10045,3],[10032,4],[10027,5],[20047,10],[20027,11],[30030,12],[30023,17],[40027,18]]</v>
+        <v>[[10042,2],[10040,3],[10043,4],[20046,10],[30032,11],[40029,17]]</v>
       </c>
       <c r="H200">
         <v>3.67</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="str">
-        <v>[[10037,3],[10045,4],[10032,10],[10027,11],[20047,17],[20027,18],[30030,12],[30023,5],[40027,19]]</v>
+        <v>[[10031,3],[10028,4],[10038,5],[20044,10],[30026,11],[40027,18]]</v>
       </c>
       <c r="H201">
         <v>3.67</v>
@@ -6245,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="str">
-        <v>[[10037,2],[10045,3],[10032,4],[10027,5],[20047,10],[20027,11],[30030,12],[30023,17],[40027,18]]</v>
+        <v>[[10046,3],[10041,4],[10037,10],[20041,11],[30028,17],[40025,18]]</v>
       </c>
       <c r="H202">
         <v>3.67</v>
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="str">
-        <v>[[10037,3],[10045,4],[10032,10],[10027,11],[20047,17],[20027,18],[30030,12],[30023,5],[40027,19]]</v>
+        <v>[[10048,2],[10047,3],[10027,4],[20040,10],[30025,11],[40030,17]]</v>
       </c>
       <c r="H203">
         <v>3.67</v>
@@ -6303,7 +6303,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="str">
-        <v>[[90039,3],[90040,4],[10037,10],[10045,11],[10032,17],[10027,18],[10048,12],[10042,5],[20047,19],[20027,2],[20043,9],[30030,16],[30023,20],[30025,6],[40027,13],[40032,25]]</v>
+        <v>[[90039,3],[90040,4],[10044,10],[10045,11],[10039,17],[20043,18],[20038,12],[30031,5],[30030,19],[40032,2],[40031,9]]</v>
       </c>
       <c r="H204">
         <v>5.65</v>
